--- a/excel/云下/云下物料.xlsx
+++ b/excel/云下/云下物料.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="727">
   <si>
     <t/>
   </si>
@@ -34,7 +34,7 @@
     <t>价格</t>
   </si>
   <si>
-    <t>供应商</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>档口</t>
@@ -91,7 +91,7 @@
     <t>瓶</t>
   </si>
   <si>
-    <t>调料</t>
+    <t>调料类</t>
   </si>
   <si>
     <t>350g</t>
@@ -127,7 +127,7 @@
     <t>粮油</t>
   </si>
   <si>
-    <t>1袋=25kg 1kg=1000g</t>
+    <t xml:space="preserve">1袋=25kg </t>
   </si>
   <si>
     <t>255</t>
@@ -1288,13 +1288,10 @@
     <t>地板清洁剂</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>2001013</t>
   </si>
   <si>
-    <t>订书针</t>
+    <t>订书订</t>
   </si>
   <si>
     <t>1.5</t>
@@ -1348,7 +1345,10 @@
     <t>2001022</t>
   </si>
   <si>
-    <t>美泽保鲜袋</t>
+    <t>美泽保鲜袋（30*20）</t>
+  </si>
+  <si>
+    <t>200只</t>
   </si>
   <si>
     <t>7.7</t>
@@ -1387,18 +1387,12 @@
     <t>600个</t>
   </si>
   <si>
-    <t>564</t>
-  </si>
-  <si>
     <t>2001028</t>
   </si>
   <si>
     <t>沙拉碗（云下500ml)</t>
   </si>
   <si>
-    <t>684</t>
-  </si>
-  <si>
     <t>2001029</t>
   </si>
   <si>
@@ -1426,18 +1420,12 @@
     <t>无纺布袋（云下）</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>2001032</t>
   </si>
   <si>
     <t>五月花厨房用纸</t>
   </si>
   <si>
-    <t>33.9</t>
-  </si>
-  <si>
     <t>2001033</t>
   </si>
   <si>
@@ -1507,9 +1495,6 @@
     <t>云下餐具包</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>2001046</t>
   </si>
   <si>
@@ -1525,18 +1510,12 @@
     <t>松毛尖</t>
   </si>
   <si>
-    <t>蔬菜类</t>
-  </si>
-  <si>
     <t>1kg</t>
   </si>
   <si>
     <t>烧烤料</t>
   </si>
   <si>
-    <t>调料类</t>
-  </si>
-  <si>
     <t>米布粉</t>
   </si>
   <si>
@@ -1738,7 +1717,7 @@
     <t>台</t>
   </si>
   <si>
-    <t>烤箱药片</t>
+    <t>烤箱清洁片</t>
   </si>
   <si>
     <t>100块</t>
@@ -1753,7 +1732,7 @@
     <t>加长胶皮手套</t>
   </si>
   <si>
-    <t>10双</t>
+    <t>1双</t>
   </si>
   <si>
     <t>兰柏文80*30</t>
@@ -2052,6 +2031,10 @@
     <t>凤梨</t>
   </si>
   <si>
+    <t xml:space="preserve">1002007
+</t>
+  </si>
+  <si>
     <t>蚕豆</t>
   </si>
   <si>
@@ -2090,7 +2073,7 @@
     <t>陈醋</t>
   </si>
   <si>
-    <t xml:space="preserve"> 蘑菇精</t>
+    <t>蘑菇精</t>
   </si>
   <si>
     <t>二荆条</t>
@@ -2114,23 +2097,112 @@
     <t>1000g*10袋</t>
   </si>
   <si>
-    <t>姜柄瓜</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 青柠巴斯克切片蛋糕</t>
   </si>
   <si>
     <t xml:space="preserve"> 生猪肉沫</t>
   </si>
   <si>
+    <t>保鲜膜(45cm）</t>
+  </si>
+  <si>
+    <t>45厘米</t>
+  </si>
+  <si>
+    <t>保鲜袋（30*40）</t>
+  </si>
+  <si>
+    <t>烤箱保养药片</t>
+  </si>
+  <si>
+    <t>蛋黄酱</t>
+  </si>
+  <si>
+    <t>手擀面</t>
+  </si>
+  <si>
+    <t>白芷</t>
+  </si>
+  <si>
+    <t>桂皮</t>
+  </si>
+  <si>
+    <t>西瓜</t>
+  </si>
+  <si>
+    <t>椰丝</t>
+  </si>
+  <si>
+    <t>紫叶生菜</t>
+  </si>
+  <si>
+    <t>冬瓜</t>
+  </si>
+  <si>
+    <t>丝瓜</t>
+  </si>
+  <si>
+    <t>海带</t>
+  </si>
+  <si>
+    <t>扁豆</t>
+  </si>
+  <si>
+    <t>球生菜</t>
+  </si>
+  <si>
+    <t>小油菜</t>
+  </si>
+  <si>
+    <t>白不老豆角</t>
+  </si>
+  <si>
+    <t>大白菜</t>
+  </si>
+  <si>
+    <t>莴笋</t>
+  </si>
+  <si>
+    <t>茼蒿</t>
+  </si>
+  <si>
+    <t>红薯</t>
+  </si>
+  <si>
+    <t>黄豆芽</t>
+  </si>
+  <si>
+    <t>蒜薹</t>
+  </si>
+  <si>
+    <t>芹菜</t>
+  </si>
+  <si>
+    <t>贡菜干</t>
+  </si>
+  <si>
+    <t>供应商</t>
+  </si>
+  <si>
     <t>包浆豆腐1</t>
   </si>
   <si>
-    <t>蘑菇精</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1002007
-</t>
+    <t>雪川土豆块</t>
+  </si>
+  <si>
+    <t>半切带皮土豆</t>
+  </si>
+  <si>
+    <t>傣家白酸笋</t>
+  </si>
+  <si>
+    <t>猪里脊</t>
+  </si>
+  <si>
+    <t>牛肉</t>
+  </si>
+  <si>
+    <t>双</t>
   </si>
 </sst>
 </file>
@@ -2140,7 +2212,7 @@
   <numFmts count="1">
     <numFmt numFmtId="300" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
@@ -2167,6 +2239,7 @@
       <color rgb="FFDE3C36"/>
       <sz val="11"/>
     </font>
+    <font/>
     <font>
       <name val="Calibri"/>
     </font>
@@ -2218,9 +2291,9 @@
     </border>
   </borders>
   <cellStyleXfs>
-    <xf numFmtId="300" fontId="10" fillId="3" borderId="1" xfId="0"/>
+    <xf numFmtId="300" fontId="11" fillId="3" borderId="1" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2231,49 +2304,52 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="300" fontId="10" fillId="3" borderId="1" xfId="0"/>
+    <xf numFmtId="300" fontId="11" fillId="3" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="300" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1"/>
+    <xf fontId="5" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" xfId="0">
+    <xf fontId="6" fillId="0" borderId="0" xfId="0">
       <alignment vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="0" xfId="0">
+    <xf fontId="7" fillId="0" borderId="0" xfId="0">
       <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf fontId="7" fillId="0" borderId="0" xfId="0">
+    <xf fontId="8" fillId="0" borderId="0" xfId="0">
       <alignment vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </xf>
-    <xf fontId="8" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf fontId="9" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" xfId="0">
+    <xf fontId="6" fillId="0" borderId="0" xfId="0">
       <alignment vertical="bottom" textRotation="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="7" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="8" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" xfId="0">
       <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </xf>
-    <xf numFmtId="300" fontId="10" fillId="3" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="9" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="300" fontId="11" fillId="3" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf fontId="9" fillId="0" borderId="0" xfId="0"/>
+    <xf fontId="10" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2604,7 +2680,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="H320"/>
+  <dimension ref="H359"/>
   <cols>
     <col min="1" max="1" width="28.2109" customWidth="1"/>
     <col min="4" max="4" width="29.3125" customWidth="1"/>
@@ -2628,8 +2704,8 @@
       <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>6</v>
+      <c r="F1" s="5" t="s">
+        <v>719</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>7</v>
@@ -2697,7 +2773,7 @@
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -2801,7 +2877,7 @@
       <c r="B8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -2946,7 +3022,7 @@
       <c r="G13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="7">
         <v>1003023</v>
       </c>
     </row>
@@ -2957,7 +3033,7 @@
       <c r="B14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -2983,7 +3059,7 @@
       <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -3002,29 +3078,29 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="24" customFormat="1">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:8" s="25" customFormat="1">
+      <c r="A16" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="D16" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="8">
+      <c r="G16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="10">
         <v>1006056</v>
       </c>
     </row>
@@ -3035,7 +3111,7 @@
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -3061,7 +3137,7 @@
       <c r="B18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -3191,7 +3267,7 @@
       <c r="B23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D23" s="4" t="s">
@@ -3243,7 +3319,7 @@
       <c r="B25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D25" s="4" t="s">
@@ -3269,7 +3345,7 @@
       <c r="B26" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -3414,7 +3490,7 @@
       <c r="G31" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="7">
         <v>1001103</v>
       </c>
     </row>
@@ -3440,7 +3516,7 @@
       <c r="G32" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="7">
         <v>1001026</v>
       </c>
     </row>
@@ -3492,7 +3568,7 @@
       <c r="G34" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="7">
         <v>1001009</v>
       </c>
     </row>
@@ -3596,7 +3672,7 @@
       <c r="G38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38" s="7">
         <v>1003022</v>
       </c>
     </row>
@@ -3622,7 +3698,7 @@
       <c r="G39" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H39" s="6">
+      <c r="H39" s="7">
         <v>1001094</v>
       </c>
     </row>
@@ -3752,7 +3828,7 @@
       <c r="G44" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H44" s="6">
+      <c r="H44" s="7">
         <v>1001098</v>
       </c>
     </row>
@@ -3778,7 +3854,7 @@
       <c r="G45" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="7">
         <v>1001096</v>
       </c>
       <c r="J45" t="s">
@@ -3859,7 +3935,7 @@
       <c r="G48" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H48" s="6">
+      <c r="H48" s="7">
         <v>1001099</v>
       </c>
     </row>
@@ -3937,7 +4013,7 @@
       <c r="G51" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H51" s="6">
+      <c r="H51" s="7">
         <v>1003021</v>
       </c>
     </row>
@@ -4015,7 +4091,7 @@
       <c r="G54" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H54" s="6">
+      <c r="H54" s="7">
         <v>1001100</v>
       </c>
     </row>
@@ -4249,7 +4325,7 @@
       <c r="G63" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H63" s="6">
+      <c r="H63" s="7">
         <v>1003024</v>
       </c>
     </row>
@@ -4301,7 +4377,7 @@
       <c r="G65" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H65" s="6">
+      <c r="H65" s="7">
         <v>1001104</v>
       </c>
     </row>
@@ -4327,7 +4403,7 @@
       <c r="G66" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H66" s="7">
         <v>1001095</v>
       </c>
     </row>
@@ -4457,7 +4533,7 @@
       <c r="G71" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H71" s="6">
+      <c r="H71" s="7">
         <v>1001102</v>
       </c>
     </row>
@@ -4639,7 +4715,7 @@
       <c r="G78" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H78" s="6">
+      <c r="H78" s="7">
         <v>1001106</v>
       </c>
     </row>
@@ -4717,7 +4793,7 @@
       <c r="G81" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H81" s="6">
+      <c r="H81" s="7">
         <v>1001105</v>
       </c>
     </row>
@@ -5029,7 +5105,7 @@
       <c r="G93" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H93" s="6">
+      <c r="H93" s="7">
         <v>1001097</v>
       </c>
     </row>
@@ -5055,7 +5131,7 @@
       <c r="G94" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H94" s="6">
+      <c r="H94" s="7">
         <v>1003025</v>
       </c>
     </row>
@@ -5092,7 +5168,7 @@
       <c r="B96" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D96" s="4" t="s">
@@ -5118,7 +5194,7 @@
       <c r="B97" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D97" s="4" t="s">
@@ -5144,7 +5220,7 @@
       <c r="B98" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D98" s="4" t="s">
@@ -5170,7 +5246,7 @@
       <c r="B99" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D99" s="4" t="s">
@@ -5196,7 +5272,7 @@
       <c r="B100" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D100" s="4" t="s">
@@ -5222,7 +5298,7 @@
       <c r="B101" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D101" s="4" t="s">
@@ -5248,7 +5324,7 @@
       <c r="B102" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D102" s="4" t="s">
@@ -5263,7 +5339,7 @@
       <c r="G102" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H102" s="6">
+      <c r="H102" s="7">
         <v>1006031</v>
       </c>
     </row>
@@ -5274,7 +5350,7 @@
       <c r="B103" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D103" s="4" t="s">
@@ -5300,7 +5376,7 @@
       <c r="B104" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D104" s="4" t="s">
@@ -5326,7 +5402,7 @@
       <c r="B105" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D105" s="4" t="s">
@@ -5352,7 +5428,7 @@
       <c r="B106" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D106" s="4" t="s">
@@ -5378,7 +5454,7 @@
       <c r="B107" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D107" s="5" t="s">
@@ -5404,7 +5480,7 @@
       <c r="B108" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D108" s="4" t="s">
@@ -5430,7 +5506,7 @@
       <c r="B109" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D109" s="4" t="s">
@@ -5456,7 +5532,7 @@
       <c r="B110" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D110" s="4" t="s">
@@ -5482,7 +5558,7 @@
       <c r="B111" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D111" s="4" t="s">
@@ -5508,7 +5584,7 @@
       <c r="B112" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D112" s="4" t="s">
@@ -5534,7 +5610,7 @@
       <c r="B113" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D113" s="4" t="s">
@@ -5560,7 +5636,7 @@
       <c r="B114" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D114" s="4" t="s">
@@ -5586,7 +5662,7 @@
       <c r="B115" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D115" s="4" t="s">
@@ -5612,7 +5688,7 @@
       <c r="B116" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D116" s="4" t="s">
@@ -5638,7 +5714,7 @@
       <c r="B117" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D117" s="4" t="s">
@@ -5664,7 +5740,7 @@
       <c r="B118" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D118" s="4" t="s">
@@ -5679,7 +5755,7 @@
       <c r="G118" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H118" s="6">
+      <c r="H118" s="7">
         <v>1006085</v>
       </c>
     </row>
@@ -5690,7 +5766,7 @@
       <c r="B119" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D119" s="4" t="s">
@@ -5716,7 +5792,7 @@
       <c r="B120" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D120" s="4" t="s">
@@ -5861,7 +5937,7 @@
       <c r="G125" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H125" s="6">
+      <c r="H125" s="7">
         <v>1009030</v>
       </c>
     </row>
@@ -6043,7 +6119,7 @@
       <c r="G132" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H132" s="6">
+      <c r="H132" s="7">
         <v>1001101</v>
       </c>
     </row>
@@ -6346,8 +6422,8 @@
       <c r="D144" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E144" s="4" t="s">
-        <v>424</v>
+      <c r="E144" s="7">
+        <v>95</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>390</v>
@@ -6356,12 +6432,12 @@
         <v>32</v>
       </c>
       <c r="H144" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="5" t="s">
         <v>425</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
-      <c r="A145" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>18</v>
@@ -6373,7 +6449,7 @@
         <v>18</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>390</v>
@@ -6382,21 +6458,21 @@
         <v>32</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B146" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>388</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>385</v>
@@ -6408,24 +6484,24 @@
         <v>32</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B147" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>433</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>388</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>65</v>
+        <v>432</v>
+      </c>
+      <c r="E147" s="7">
+        <v>25</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>390</v>
@@ -6434,12 +6510,12 @@
         <v>32</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>102</v>
@@ -6450,7 +6526,7 @@
       <c r="D148" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E148" s="6">
+      <c r="E148" s="7">
         <v>21</v>
       </c>
       <c r="F148" s="4" t="s">
@@ -6460,21 +6536,21 @@
         <v>32</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>388</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>130</v>
@@ -6486,21 +6562,21 @@
         <v>32</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>388</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>179</v>
@@ -6512,12 +6588,12 @@
         <v>32</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>112</v>
@@ -6529,7 +6605,7 @@
         <v>389</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>390</v>
@@ -6538,12 +6614,12 @@
         <v>32</v>
       </c>
       <c r="H151" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="5" t="s">
         <v>443</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
-      <c r="A152" s="4" t="s">
-        <v>444</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>405</v>
@@ -6551,8 +6627,8 @@
       <c r="C152" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D152" s="4" t="s">
-        <v>405</v>
+      <c r="D152" s="5" t="s">
+        <v>444</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>445</v>
@@ -6658,8 +6734,8 @@
       <c r="D156" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="E156" s="4" t="s">
-        <v>457</v>
+      <c r="E156" s="7">
+        <v>282</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>390</v>
@@ -6668,12 +6744,12 @@
         <v>32</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>112</v>
@@ -6684,8 +6760,8 @@
       <c r="D157" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="E157" s="4" t="s">
-        <v>460</v>
+      <c r="E157" s="7">
+        <v>228</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>390</v>
@@ -6694,12 +6770,12 @@
         <v>32</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>112</v>
@@ -6711,7 +6787,7 @@
         <v>456</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>390</v>
@@ -6720,12 +6796,12 @@
         <v>32</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>112</v>
@@ -6734,10 +6810,10 @@
         <v>388</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>390</v>
@@ -6746,12 +6822,12 @@
         <v>32</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>421</v>
@@ -6762,8 +6838,8 @@
       <c r="D160" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="E160" s="4" t="s">
-        <v>470</v>
+      <c r="E160" s="7">
+        <v>0.9</v>
       </c>
       <c r="F160" s="4" t="s">
         <v>390</v>
@@ -6772,12 +6848,12 @@
         <v>32</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="4" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>102</v>
@@ -6788,8 +6864,8 @@
       <c r="D161" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E161" s="4" t="s">
-        <v>473</v>
+      <c r="E161" s="7">
+        <v>11.3</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>390</v>
@@ -6798,12 +6874,12 @@
         <v>32</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="4" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>112</v>
@@ -6815,7 +6891,7 @@
         <v>389</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>390</v>
@@ -6824,12 +6900,12 @@
         <v>32</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="4" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>405</v>
@@ -6841,7 +6917,7 @@
         <v>405</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>390</v>
@@ -6850,12 +6926,12 @@
         <v>32</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="4" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>411</v>
@@ -6864,10 +6940,10 @@
         <v>388</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="F164" s="4" t="s">
         <v>390</v>
@@ -6876,12 +6952,12 @@
         <v>32</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="4" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>112</v>
@@ -6893,7 +6969,7 @@
         <v>389</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>390</v>
@@ -6902,12 +6978,12 @@
         <v>32</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="4" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>112</v>
@@ -6916,10 +6992,10 @@
         <v>388</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>390</v>
@@ -6928,12 +7004,12 @@
         <v>32</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>421</v>
@@ -6945,7 +7021,7 @@
         <v>421</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>390</v>
@@ -6954,12 +7030,12 @@
         <v>32</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>112</v>
@@ -6970,7 +7046,7 @@
       <c r="D168" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E168" s="6">
+      <c r="E168" s="7">
         <v>155</v>
       </c>
       <c r="F168" s="4" t="s">
@@ -6980,12 +7056,12 @@
         <v>32</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="4" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>112</v>
@@ -6994,10 +7070,10 @@
         <v>388</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="E169" s="4" t="s">
-        <v>497</v>
+        <v>484</v>
+      </c>
+      <c r="E169" s="7">
+        <v>370</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>390</v>
@@ -7006,12 +7082,12 @@
         <v>32</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="4" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>112</v>
@@ -7020,7 +7096,7 @@
         <v>388</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>150</v>
@@ -7032,21 +7108,21 @@
         <v>32</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="4" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="E171" s="4">
         <v>4</v>
@@ -7063,13 +7139,13 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="4" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C172" s="4" t="s">
-        <v>506</v>
+      <c r="C172" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>12</v>
@@ -7089,7 +7165,7 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="4" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>35</v>
@@ -7115,16 +7191,16 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="4" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>276</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>509</v>
+        <v>341</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="E174" s="4">
         <v>150</v>
@@ -7141,13 +7217,13 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="4" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>12</v>
@@ -7167,7 +7243,7 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="4" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>10</v>
@@ -7193,13 +7269,13 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="4" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>12</v>
@@ -7219,13 +7295,13 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="4" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>12</v>
@@ -7245,13 +7321,13 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="4" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C179" s="4" t="s">
-        <v>506</v>
+      <c r="C179" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>12</v>
@@ -7271,13 +7347,13 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="4" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>12</v>
@@ -7297,13 +7373,13 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="4" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>12</v>
@@ -7323,7 +7399,7 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="4" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>10</v>
@@ -7349,13 +7425,13 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="4" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>12</v>
@@ -7375,13 +7451,13 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="4" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>421</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>421</v>
@@ -7401,13 +7477,13 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="4" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>12</v>
@@ -7427,13 +7503,13 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="4" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>12</v>
@@ -7453,13 +7529,13 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187" s="4" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>12</v>
@@ -7479,13 +7555,13 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="4" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>12</v>
@@ -7505,13 +7581,13 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189" s="4" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>12</v>
@@ -7531,13 +7607,13 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="4" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>12</v>
@@ -7557,13 +7633,13 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="4" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>12</v>
@@ -7583,13 +7659,13 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="4" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>12</v>
@@ -7609,13 +7685,13 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="4" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="B193" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>12</v>
@@ -7635,13 +7711,13 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194" s="4" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>531</v>
+        <v>372</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>12</v>
@@ -7661,13 +7737,13 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="4" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>12</v>
@@ -7687,13 +7763,13 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="4" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D196" s="4" t="s">
         <v>202</v>
@@ -7713,13 +7789,13 @@
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="4" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>12</v>
@@ -7739,13 +7815,13 @@
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="4" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>12</v>
@@ -7765,13 +7841,13 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="4" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>12</v>
@@ -7791,13 +7867,13 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="4" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>538</v>
+        <v>36</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>12</v>
@@ -7817,13 +7893,13 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="4" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>12</v>
@@ -7843,13 +7919,13 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="4" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>12</v>
@@ -7869,13 +7945,13 @@
     </row>
     <row r="203" spans="1:8">
       <c r="A203" s="4" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>12</v>
@@ -7895,13 +7971,13 @@
     </row>
     <row r="204" spans="1:8">
       <c r="A204" s="4" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>531</v>
+        <v>372</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>12</v>
@@ -7921,13 +7997,13 @@
     </row>
     <row r="205" spans="1:8">
       <c r="A205" s="4" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="B205" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>12</v>
@@ -7947,13 +8023,13 @@
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="4" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D206" s="4" t="s">
         <v>12</v>
@@ -7973,13 +8049,13 @@
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="4" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D207" s="4" t="s">
         <v>12</v>
@@ -7999,7 +8075,7 @@
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="4" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>10</v>
@@ -8025,13 +8101,13 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="4" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="B209" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D209" s="4" t="s">
         <v>12</v>
@@ -8051,13 +8127,13 @@
     </row>
     <row r="210" spans="1:8">
       <c r="A210" s="4" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>531</v>
+        <v>372</v>
       </c>
       <c r="D210" s="4" t="s">
         <v>12</v>
@@ -8077,13 +8153,13 @@
     </row>
     <row r="211" spans="1:8">
       <c r="A211" s="4" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>12</v>
@@ -8103,13 +8179,13 @@
     </row>
     <row r="212" spans="1:8">
       <c r="A212" s="4" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>12</v>
@@ -8129,7 +8205,7 @@
     </row>
     <row r="213" spans="1:8">
       <c r="A213" s="4" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="B213" s="4" t="s">
         <v>10</v>
@@ -8155,13 +8231,13 @@
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="4" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="B214" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>12</v>
@@ -8181,16 +8257,16 @@
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="4" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E215" s="4">
         <v>235</v>
@@ -8207,16 +8283,16 @@
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="4" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="B216" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="E216" s="4">
         <v>23</v>
@@ -8233,16 +8309,16 @@
     </row>
     <row r="217" spans="1:8">
       <c r="A217" s="4" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="E217" s="4">
         <v>47.5</v>
@@ -8259,7 +8335,7 @@
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="4" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>112</v>
@@ -8285,7 +8361,7 @@
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="4" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>102</v>
@@ -8294,7 +8370,7 @@
         <v>388</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="E219" s="4">
         <v>0.24</v>
@@ -8311,7 +8387,7 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="4" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B220" s="4" t="s">
         <v>102</v>
@@ -8320,7 +8396,7 @@
         <v>388</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="E220" s="4">
         <v>0.95</v>
@@ -8337,7 +8413,7 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="4" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>102</v>
@@ -8346,7 +8422,7 @@
         <v>388</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="E221" s="4">
         <v>15</v>
@@ -8363,16 +8439,16 @@
     </row>
     <row r="222" spans="1:8">
       <c r="A222" s="4" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>388</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="E222" s="4">
         <v>2.8</v>
@@ -8389,7 +8465,7 @@
     </row>
     <row r="223" spans="1:8">
       <c r="A223" s="4" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>276</v>
@@ -8398,7 +8474,7 @@
         <v>388</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="E223" s="4">
         <v>45</v>
@@ -8415,7 +8491,7 @@
     </row>
     <row r="224" spans="1:8">
       <c r="A224" s="4" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>18</v>
@@ -8424,10 +8500,10 @@
         <v>388</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="E224" s="4">
-        <v>32</v>
+        <v>495</v>
+      </c>
+      <c r="E224" s="7">
+        <v>28</v>
       </c>
       <c r="F224" s="4" t="s">
         <v>390</v>
@@ -8441,7 +8517,7 @@
     </row>
     <row r="225" spans="1:8">
       <c r="A225" s="4" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>102</v>
@@ -8450,7 +8526,7 @@
         <v>388</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="E225" s="4">
         <v>18</v>
@@ -8467,16 +8543,16 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="4" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>388</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="E226" s="4">
         <v>10</v>
@@ -8492,8 +8568,8 @@
       </c>
     </row>
     <row r="227" spans="1:8">
-      <c r="A227" s="4" t="s">
-        <v>574</v>
+      <c r="A227" s="5" t="s">
+        <v>567</v>
       </c>
       <c r="B227" s="4" t="s">
         <v>18</v>
@@ -8502,7 +8578,7 @@
         <v>388</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="E227" s="4">
         <v>580</v>
@@ -8519,7 +8595,7 @@
     </row>
     <row r="228" spans="1:8">
       <c r="A228" s="4" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>112</v>
@@ -8545,7 +8621,7 @@
     </row>
     <row r="229" spans="1:8">
       <c r="A229" s="4" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>102</v>
@@ -8571,19 +8647,19 @@
     </row>
     <row r="230" spans="1:8">
       <c r="A230" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="B230" s="4" t="s">
-        <v>102</v>
+        <v>571</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>726</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D230" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="E230" s="4">
-        <v>32</v>
+      <c r="D230" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="E230" s="7">
+        <v>10</v>
       </c>
       <c r="F230" s="4" t="s">
         <v>390</v>
@@ -8597,7 +8673,7 @@
     </row>
     <row r="231" spans="1:8">
       <c r="A231" s="4" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="B231" s="4" t="s">
         <v>112</v>
@@ -8606,7 +8682,7 @@
         <v>388</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="E231" s="4">
         <v>114</v>
@@ -8623,7 +8699,7 @@
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="4" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B232" s="4" t="s">
         <v>112</v>
@@ -8632,10 +8708,10 @@
         <v>388</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="E232" s="4">
-        <v>114</v>
+        <v>464</v>
+      </c>
+      <c r="E232" s="7">
+        <v>66</v>
       </c>
       <c r="F232" s="4" t="s">
         <v>390</v>
@@ -8649,7 +8725,7 @@
     </row>
     <row r="233" spans="1:8">
       <c r="A233" s="4" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="B233" s="4" t="s">
         <v>112</v>
@@ -8658,10 +8734,10 @@
         <v>388</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="E233" s="4">
-        <v>132</v>
+        <v>464</v>
+      </c>
+      <c r="E233" s="7">
+        <v>114</v>
       </c>
       <c r="F233" s="4" t="s">
         <v>390</v>
@@ -8675,7 +8751,7 @@
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="4" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="B234" s="4" t="s">
         <v>276</v>
@@ -8684,7 +8760,7 @@
         <v>388</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E234" s="4">
         <v>95</v>
@@ -8701,7 +8777,7 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" s="4" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>112</v>
@@ -8710,7 +8786,7 @@
         <v>388</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="E235" s="4">
         <v>170</v>
@@ -8727,7 +8803,7 @@
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="4" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B236" s="4" t="s">
         <v>102</v>
@@ -8736,7 +8812,7 @@
         <v>388</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="E236" s="4">
         <v>27</v>
@@ -8753,7 +8829,7 @@
     </row>
     <row r="237" spans="1:8">
       <c r="A237" s="4" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="B237" s="4" t="s">
         <v>45</v>
@@ -8762,7 +8838,7 @@
         <v>106</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="E237" s="4">
         <v>15</v>
@@ -8779,7 +8855,7 @@
     </row>
     <row r="238" spans="1:8">
       <c r="A238" s="4" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="B238" s="4" t="s">
         <v>276</v>
@@ -8788,7 +8864,7 @@
         <v>106</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="E238" s="4">
         <v>28</v>
@@ -8805,13 +8881,13 @@
     </row>
     <row r="239" spans="1:8">
       <c r="A239" s="4" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="B239" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C239" s="4" t="s">
-        <v>506</v>
+      <c r="C239" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D239" s="4">
         <v>200</v>
@@ -8831,13 +8907,13 @@
     </row>
     <row r="240" spans="1:8">
       <c r="A240" s="4" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="B240" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C240" s="4" t="s">
-        <v>506</v>
+      <c r="C240" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>95</v>
@@ -8862,8 +8938,8 @@
       <c r="B241" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C241" s="4" t="s">
-        <v>506</v>
+      <c r="C241" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D241" s="4" t="s">
         <v>330</v>
@@ -8883,16 +8959,16 @@
     </row>
     <row r="242" spans="1:8">
       <c r="A242" s="4" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="B242" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C242" s="4" t="s">
-        <v>506</v>
+      <c r="C242" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="E242" s="4">
         <v>13</v>
@@ -8909,16 +8985,16 @@
     </row>
     <row r="243" spans="1:8">
       <c r="A243" s="4" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="B243" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C243" s="4" t="s">
-        <v>506</v>
+      <c r="C243" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E243" s="4">
         <v>13.5</v>
@@ -8935,16 +9011,16 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="4" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B244" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C244" s="4" t="s">
-        <v>506</v>
+      <c r="C244" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="E244" s="4">
         <v>92</v>
@@ -8961,13 +9037,13 @@
     </row>
     <row r="245" spans="1:8">
       <c r="A245" s="4" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="B245" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C245" s="4" t="s">
-        <v>506</v>
+      <c r="C245" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D245" s="4" t="s">
         <v>12</v>
@@ -8987,16 +9063,16 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="4" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="B246" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C246" s="4" t="s">
-        <v>506</v>
+      <c r="C246" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="E246" s="4">
         <v>9</v>
@@ -9013,16 +9089,16 @@
     </row>
     <row r="247" spans="1:8">
       <c r="A247" s="4" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C247" s="4" t="s">
-        <v>506</v>
+      <c r="C247" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="E247" s="4">
         <v>26</v>
@@ -9039,7 +9115,7 @@
     </row>
     <row r="248" spans="1:8">
       <c r="A248" s="4" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="B248" s="4" t="s">
         <v>24</v>
@@ -9065,7 +9141,7 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249" s="4" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>18</v>
@@ -9091,22 +9167,22 @@
     </row>
     <row r="250" spans="1:8">
       <c r="A250" s="4" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="B250" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>509</v>
+        <v>341</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="E250" s="4">
         <v>180</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>109</v>
@@ -9117,22 +9193,22 @@
     </row>
     <row r="251" spans="1:8">
       <c r="A251" s="4" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="B251" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>509</v>
+        <v>341</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="E251" s="4">
         <v>68</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>109</v>
@@ -9143,22 +9219,22 @@
     </row>
     <row r="252" spans="1:8">
       <c r="A252" s="4" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="B252" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>509</v>
+        <v>341</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="E252" s="4">
         <v>80</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>109</v>
@@ -9169,7 +9245,7 @@
     </row>
     <row r="253" spans="1:8">
       <c r="A253" s="4" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="B253" s="4" t="s">
         <v>35</v>
@@ -9178,7 +9254,7 @@
         <v>106</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="E253" s="4">
         <v>3.5</v>
@@ -9195,7 +9271,7 @@
     </row>
     <row r="254" spans="1:8">
       <c r="A254" s="4" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="B254" s="4" t="s">
         <v>45</v>
@@ -9204,7 +9280,7 @@
         <v>106</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="E254" s="4">
         <v>12</v>
@@ -9221,7 +9297,7 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255" s="4" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="B255" s="4" t="s">
         <v>112</v>
@@ -9230,7 +9306,7 @@
         <v>106</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="E255" s="4">
         <v>297.5</v>
@@ -9247,7 +9323,7 @@
     </row>
     <row r="256" spans="1:8">
       <c r="A256" s="4" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="B256" s="4" t="s">
         <v>35</v>
@@ -9256,13 +9332,13 @@
         <v>19</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="E256" s="4">
         <v>4.5</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="G256" s="4" t="s">
         <v>109</v>
@@ -9273,16 +9349,16 @@
     </row>
     <row r="257" spans="1:8">
       <c r="A257" s="4" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="B257" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C257" s="4" t="s">
+      <c r="C257" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="E257" s="4">
         <v>8</v>
@@ -9291,7 +9367,7 @@
         <v>271</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="H257" s="4">
         <v>1006062</v>
@@ -9299,7 +9375,7 @@
     </row>
     <row r="258" spans="1:8">
       <c r="A258" s="4" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="B258" s="4" t="s">
         <v>10</v>
@@ -9314,10 +9390,10 @@
         <v>14.5</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="H258" s="4">
         <v>1006067</v>
@@ -9325,7 +9401,7 @@
     </row>
     <row r="259" spans="1:8">
       <c r="A259" s="4" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="B259" s="4" t="s">
         <v>35</v>
@@ -9340,10 +9416,10 @@
         <v>32</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="H259" s="4">
         <v>1009027</v>
@@ -9351,16 +9427,16 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260" s="4" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="B260" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C260" s="4" t="s">
+      <c r="C260" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="E260" s="4">
         <v>226</v>
@@ -9369,1517 +9445,2434 @@
         <v>271</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="H260" s="4">
         <v>1005009</v>
       </c>
     </row>
     <row r="261" spans="1:8">
-      <c r="A261" s="9" t="s">
+      <c r="A261" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="B261" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D261" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E261" s="6">
+        <v>48.5</v>
+      </c>
+      <c r="F261" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="G261" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H261" s="11">
+        <v>1006010</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="A262" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="B262" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D262" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E262" s="6">
+        <v>43</v>
+      </c>
+      <c r="F262" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G262" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H262" s="11">
+        <v>1003017</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="B263" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D263" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E263" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="F263" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G263" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H263" s="11">
+        <v>1009012</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="B264" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D264" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="E264" s="6">
+        <v>30</v>
+      </c>
+      <c r="F264" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="G264" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H264" s="11">
+        <v>1007013</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="A265" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="B265" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D265" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E265" s="6">
+        <v>23</v>
+      </c>
+      <c r="F265" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G265" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H265" s="11">
+        <v>1006049</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="B266" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D266" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E266" s="6">
+        <v>45</v>
+      </c>
+      <c r="F266" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G266" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H266" s="11">
+        <v>1006002</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="B261" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C261" s="10" t="s">
+      <c r="B267" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C267" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D261" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E261" s="10">
-        <v>48.5</v>
-      </c>
-      <c r="F261" s="10" t="s">
-        <v>623</v>
-      </c>
-      <c r="G261" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H261" s="9">
-        <v>1006010</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8">
-      <c r="A262" s="9" t="s">
+      <c r="D267" s="11" t="s">
         <v>629</v>
       </c>
-      <c r="B262" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C262" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D262" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E262" s="10">
-        <v>43</v>
-      </c>
-      <c r="F262" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G262" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H262" s="9">
-        <v>1003017</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8">
-      <c r="A263" s="9" t="s">
+      <c r="E267" s="6">
+        <v>117.6</v>
+      </c>
+      <c r="F267" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="B263" s="9" t="s">
+      <c r="G267" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H267" s="11">
+        <v>1006034</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8">
+      <c r="A268" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="B268" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C263" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D263" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E263" s="10">
-        <v>9.5</v>
-      </c>
-      <c r="F263" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G263" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H263" s="9">
-        <v>1009012</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8">
-      <c r="A264" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="B264" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C264" s="10" t="s">
+      <c r="C268" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D264" s="9" t="s">
+      <c r="D268" s="11" t="s">
         <v>632</v>
       </c>
-      <c r="E264" s="10">
-        <v>30</v>
-      </c>
-      <c r="F264" s="10" t="s">
-        <v>608</v>
-      </c>
-      <c r="G264" s="12" t="s">
+      <c r="E268" s="6">
+        <v>38</v>
+      </c>
+      <c r="F268" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="G268" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H264" s="9">
-        <v>1007013</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8">
-      <c r="A265" s="9" t="s">
+      <c r="H268" s="11">
+        <v>1008015</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8">
+      <c r="A269" s="11" t="s">
         <v>633</v>
       </c>
-      <c r="B265" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C265" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D265" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E265" s="10">
-        <v>23</v>
-      </c>
-      <c r="F265" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G265" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H265" s="9">
-        <v>1006049</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8">
-      <c r="A266" s="9" t="s">
+      <c r="B269" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D269" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E269" s="6">
+        <v>255</v>
+      </c>
+      <c r="F269" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="B266" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C266" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D266" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E266" s="10">
-        <v>45</v>
-      </c>
-      <c r="F266" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G266" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H266" s="9">
-        <v>1006002</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8">
-      <c r="A267" s="9" t="s">
+      <c r="G269" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="B267" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C267" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D267" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="E267" s="10">
-        <v>117.6</v>
-      </c>
-      <c r="F267" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="G267" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H267" s="9">
-        <v>1006034</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8">
-      <c r="A268" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="B268" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C268" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D268" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="E268" s="10">
-        <v>38</v>
-      </c>
-      <c r="F268" s="10" t="s">
-        <v>608</v>
-      </c>
-      <c r="G268" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H268" s="9">
-        <v>1008015</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8">
-      <c r="A269" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="B269" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C269" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D269" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E269" s="10">
-        <v>255</v>
-      </c>
-      <c r="F269" s="10" t="s">
-        <v>641</v>
-      </c>
-      <c r="G269" s="11" t="s">
-        <v>642</v>
-      </c>
-      <c r="H269" s="9">
+      <c r="H269" s="11">
         <v>1006064</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C270" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D270" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E270" s="7">
+        <v>26</v>
+      </c>
+      <c r="F270" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="G270" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H270" s="7">
+        <v>1006084</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8">
+      <c r="A271" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="B271" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D271" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E271" s="16">
+        <v>18</v>
+      </c>
+      <c r="F271" s="15" t="s">
+        <v>616</v>
+      </c>
+      <c r="G271" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="H271" s="16">
+        <v>1006070</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8">
+      <c r="A272" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="B272" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D272" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E272" s="11">
+        <v>20</v>
+      </c>
+      <c r="F272" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="G272" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H272" s="17">
+        <v>1001107</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
+      <c r="A273" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="B273" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D273" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E273" s="11">
+        <v>20</v>
+      </c>
+      <c r="F273" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="G273" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H273" s="17">
+        <v>1001108</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="A274" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="B274" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C274" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D274" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E274" s="11">
+        <v>50</v>
+      </c>
+      <c r="F274" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G274" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H274" s="17">
+        <v>1006086</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8">
+      <c r="A275" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="B275" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="B270" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C270" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="D270" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E270" s="6">
+      <c r="C275" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D275" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E275" s="11">
+        <v>90</v>
+      </c>
+      <c r="F275" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="G275" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="H275" s="6">
+        <v>1001109</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8">
+      <c r="A276" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="B276" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D276" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E276" s="11">
+        <v>50</v>
+      </c>
+      <c r="F276" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G276" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H276" s="17">
+        <v>1006001</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8">
+      <c r="A277" s="18" t="s">
+        <v>647</v>
+      </c>
+      <c r="B277" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D277" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="E277" s="11">
+        <v>43.5</v>
+      </c>
+      <c r="F277" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G277" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H277" s="17">
+        <v>1009016</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8">
+      <c r="A278" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="B278" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C278" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D278" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E278" s="11">
+        <v>38</v>
+      </c>
+      <c r="F278" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G278" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H278" s="17">
+        <v>1005015</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8">
+      <c r="A279" s="11" t="s">
+        <v>649</v>
+      </c>
+      <c r="B279" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D279" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E279" s="11">
+        <v>62</v>
+      </c>
+      <c r="F279" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G279" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H279" s="20" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8">
+      <c r="A280" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="B280" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D280" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E280" s="11">
+        <v>8</v>
+      </c>
+      <c r="F280" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G280" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H280" s="17">
+        <v>1009036</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8">
+      <c r="A281" s="21" t="s">
+        <v>652</v>
+      </c>
+      <c r="B281" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D281" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E281" s="11">
+        <v>10</v>
+      </c>
+      <c r="F281" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G281" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H281" s="17">
+        <v>1009035</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8">
+      <c r="A282" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="B282" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D282" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E282" s="11">
+        <v>5</v>
+      </c>
+      <c r="F282" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G282" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H282" s="17">
+        <v>1001038</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8">
+      <c r="A283" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="B283" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D283" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E283" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F283" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G283" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H283" s="17">
+        <v>1001110</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8">
+      <c r="A284" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="B284" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D284" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E284" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F284" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G284" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H284" s="17">
+        <v>1001111</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8">
+      <c r="A285" s="11" t="s">
+        <v>656</v>
+      </c>
+      <c r="B285" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D285" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E285" s="11">
+        <v>180</v>
+      </c>
+      <c r="F285" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G285" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H285" s="17">
+        <v>1007014</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8">
+      <c r="A286" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="B286" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D286" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E286" s="11">
+        <v>150</v>
+      </c>
+      <c r="F286" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G286" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H286" s="20" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8">
+      <c r="A287" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="B287" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D287" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E287" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F287" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G287" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H287" s="20" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8">
+      <c r="A288" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="B288" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C288" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D288" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E288" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="F288" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G288" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H288" s="17">
+        <v>1003301</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9">
+      <c r="A289" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="B289" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D289" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E289" s="11">
+        <v>8</v>
+      </c>
+      <c r="F289" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G289" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H289" s="17">
+        <v>1001113</v>
+      </c>
+      <c r="I289" s="17" t="s"/>
+    </row>
+    <row r="290" spans="1:8">
+      <c r="A290" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="B290" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D290" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E290" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F290" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G290" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H290" s="17">
+        <v>1001050</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8">
+      <c r="A291" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="B291" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D291" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E291" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F291" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G291" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H291" s="17">
+        <v>1001114</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8">
+      <c r="A292" s="11" t="s">
+        <v>665</v>
+      </c>
+      <c r="B292" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D292" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E292" s="11">
+        <v>5</v>
+      </c>
+      <c r="F292" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G292" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H292" s="17">
+        <v>1001115</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8">
+      <c r="A293" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="B293" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C293" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D293" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E293" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="F293" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G293" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H293" s="17">
+        <v>1003012</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8">
+      <c r="A294" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="B294" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D294" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E294" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="F294" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G294" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H294" s="17">
+        <v>1002005</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8">
+      <c r="A295" s="11" t="s">
+        <v>668</v>
+      </c>
+      <c r="B295" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D295" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E295" s="11">
+        <v>16</v>
+      </c>
+      <c r="F295" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G295" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H295" s="17">
+        <v>1001116</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8">
+      <c r="A296" s="11" t="s">
+        <v>669</v>
+      </c>
+      <c r="B296" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D296" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E296" s="11">
+        <v>8.6</v>
+      </c>
+      <c r="F296" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G296" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H296" s="20" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
+      <c r="A297" s="11" t="s">
+        <v>671</v>
+      </c>
+      <c r="B297" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D297" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E297" s="11">
+        <v>20</v>
+      </c>
+      <c r="F297" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G297" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H297" s="17">
+        <v>1001117</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="B298" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D298" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E298" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="F298" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G298" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H298" s="17">
+        <v>1001118</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
+      <c r="A299" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="B299" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C299" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D299" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E299" s="11">
+        <v>32.8</v>
+      </c>
+      <c r="F299" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G299" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H299" s="17">
+        <v>1001119</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
+      <c r="A300" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="B300" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D300" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E300" s="11">
+        <v>4</v>
+      </c>
+      <c r="F300" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G300" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H300" s="17">
+        <v>1001120</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8">
+      <c r="A301" s="11" t="s">
+        <v>675</v>
+      </c>
+      <c r="B301" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C301" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D301" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E301" s="11">
+        <v>5</v>
+      </c>
+      <c r="F301" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G301" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H301" s="17">
+        <v>1005005</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
+      <c r="A302" s="11" t="s">
+        <v>676</v>
+      </c>
+      <c r="B302" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D302" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E302" s="11">
+        <v>48</v>
+      </c>
+      <c r="F302" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G302" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H302" s="20" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
+      <c r="A303" s="11" t="s">
+        <v>678</v>
+      </c>
+      <c r="B303" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="C303" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D303" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E303" s="11">
+        <v>27.1</v>
+      </c>
+      <c r="F303" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G303" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H303" s="17">
+        <v>1006087</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
+      <c r="A304" s="11" t="s">
+        <v>679</v>
+      </c>
+      <c r="B304" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C304" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="D304" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="E304" s="11">
+        <v>240</v>
+      </c>
+      <c r="F304" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G304" s="19" t="s">
+        <v>680</v>
+      </c>
+      <c r="H304" s="17">
+        <v>2001060</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
+      <c r="A305" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="B305" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C305" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="D305" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="E305" s="11">
+        <v>98</v>
+      </c>
+      <c r="F305" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G305" s="19" t="s">
+        <v>680</v>
+      </c>
+      <c r="H305" s="17">
+        <v>2001061</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8">
+      <c r="A306" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="B306" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C306" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D306" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E306" s="11">
         <v>26</v>
       </c>
-      <c r="F270" s="5" t="s">
-        <v>623</v>
-      </c>
-      <c r="G270" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H270" s="6">
-        <v>1006084</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8">
-      <c r="A271" s="13" t="s">
-        <v>644</v>
-      </c>
-      <c r="B271" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C271" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D271" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E271" s="14">
+      <c r="F306" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="G306" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H306" s="17">
+        <v>1006088</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8">
+      <c r="A307" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="B307" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C307" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D307" s="11" t="s"/>
+      <c r="E307" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="F307" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="G307" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H307" s="17">
+        <v>1006089</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8">
+      <c r="A308" s="11" t="s">
+        <v>684</v>
+      </c>
+      <c r="B308" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C308" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D308" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E308" s="11">
+        <v>22</v>
+      </c>
+      <c r="F308" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G308" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H308" s="17">
+        <v>1006090</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8">
+      <c r="A309" s="11" t="s">
+        <v>685</v>
+      </c>
+      <c r="B309" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C309" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D309" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E309" s="11">
+        <v>48</v>
+      </c>
+      <c r="F309" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="G309" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H309" s="17">
+        <v>1006091</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8">
+      <c r="A310" s="11" t="s">
+        <v>686</v>
+      </c>
+      <c r="B310" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C310" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D310" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E310" s="11">
+        <v>110</v>
+      </c>
+      <c r="F310" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="G310" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="H310" s="17">
+        <v>1007022</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8">
+      <c r="A311" s="11" t="s">
+        <v>687</v>
+      </c>
+      <c r="B311" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C311" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D311" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E311" s="11">
+        <v>68</v>
+      </c>
+      <c r="F311" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="G311" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="H311" s="17">
+        <v>1007023</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8">
+      <c r="A312" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="B312" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C312" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D312" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E312" s="11">
+        <v>32</v>
+      </c>
+      <c r="F312" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G312" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H312" s="17">
+        <v>1006063</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8">
+      <c r="A313" s="11" t="s">
+        <v>689</v>
+      </c>
+      <c r="B313" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C313" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D313" s="11" t="s">
+        <v>690</v>
+      </c>
+      <c r="E313" s="11">
+        <v>450</v>
+      </c>
+      <c r="F313" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="G313" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H313" s="17">
+        <v>1006092</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8">
+      <c r="A314" s="11" t="s">
+        <v>691</v>
+      </c>
+      <c r="B314" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="C314" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D314" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="E314" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="F314" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="G314" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="H314" s="17">
+        <v>1009031</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8">
+      <c r="A315" s="11" t="s">
+        <v>692</v>
+      </c>
+      <c r="B315" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C315" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D315" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E315" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="F315" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G315" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H315" s="17">
+        <v>1003005</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8">
+      <c r="A316" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="B316" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="C316" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="D316" s="11" t="s">
+        <v>694</v>
+      </c>
+      <c r="E316" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="F316" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G316" s="19" t="s">
+        <v>680</v>
+      </c>
+      <c r="H316" s="17">
+        <v>2001062</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8">
+      <c r="A317" s="11" t="s">
+        <v>695</v>
+      </c>
+      <c r="B317" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C317" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="D317" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="E317" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="F317" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G317" s="19" t="s">
+        <v>680</v>
+      </c>
+      <c r="H317" s="17">
+        <v>2001063</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8">
+      <c r="A318" s="11" t="s">
+        <v>696</v>
+      </c>
+      <c r="B318" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="C318" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="D318" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="E318" s="11">
+        <v>630</v>
+      </c>
+      <c r="F318" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="G318" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H318" s="17">
+        <v>2001064</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8">
+      <c r="A319" s="11" t="s">
+        <v>697</v>
+      </c>
+      <c r="B319" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C319" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D319" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E319" s="11">
+        <v>23</v>
+      </c>
+      <c r="F319" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="G319" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H319" s="17">
+        <v>1006093</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8">
+      <c r="A320" s="11" t="s">
+        <v>698</v>
+      </c>
+      <c r="B320" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D320" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E320" s="11">
+        <v>8</v>
+      </c>
+      <c r="F320" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G320" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H320" s="17">
+        <v>1001200</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
+      <c r="A321" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="B321" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D321" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E321" s="11">
         <v>18</v>
       </c>
-      <c r="F271" s="13" t="s">
-        <v>623</v>
-      </c>
-      <c r="G271" s="13" t="s">
-        <v>621</v>
-      </c>
-      <c r="H271" s="14">
-        <v>1006070</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8">
-      <c r="A272" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="B272" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C272" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D272" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E272" s="9">
-        <v>20</v>
-      </c>
-      <c r="F272" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="G272" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H272" s="16">
-        <v>1001107</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8">
-      <c r="A273" s="9" t="s">
-        <v>646</v>
-      </c>
-      <c r="B273" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C273" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D273" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E273" s="9">
-        <v>20</v>
-      </c>
-      <c r="F273" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="G273" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H273" s="16">
-        <v>1001108</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8">
-      <c r="A274" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="B274" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C274" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D274" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="E274" s="9">
-        <v>50</v>
-      </c>
-      <c r="F274" s="9" t="s">
+      <c r="F321" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G321" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H321" s="17">
+        <v>1001201</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
+      <c r="A322" s="11" t="s">
+        <v>700</v>
+      </c>
+      <c r="B322" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D322" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E322" s="11">
+        <v>18</v>
+      </c>
+      <c r="F322" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G322" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H322" s="17">
+        <v>1001202</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
+      <c r="A323" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="B323" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D323" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E323" s="11">
+        <v>3</v>
+      </c>
+      <c r="F323" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G323" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H323" s="17">
+        <v>1001203</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
+      <c r="A324" s="11" t="s">
+        <v>702</v>
+      </c>
+      <c r="B324" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D324" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E324" s="11">
+        <v>8</v>
+      </c>
+      <c r="F324" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G324" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H324" s="17">
+        <v>1001204</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8">
+      <c r="A325" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="B325" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D325" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E325" s="11">
+        <v>8</v>
+      </c>
+      <c r="F325" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G325" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H325" s="17">
+        <v>1001205</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8">
+      <c r="A326" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="B326" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D326" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E326" s="11">
+        <v>3</v>
+      </c>
+      <c r="F326" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G326" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H326" s="17">
+        <v>1001206</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8">
+      <c r="A327" s="11" t="s">
+        <v>705</v>
+      </c>
+      <c r="B327" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C327" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D327" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E327" s="11">
+        <v>3</v>
+      </c>
+      <c r="F327" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G327" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H327" s="17">
+        <v>1001207</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8">
+      <c r="A328" s="11" t="s">
+        <v>706</v>
+      </c>
+      <c r="B328" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D328" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E328" s="11">
+        <v>18</v>
+      </c>
+      <c r="F328" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G328" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H328" s="17">
+        <v>1001208</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8">
+      <c r="A329" s="11" t="s">
+        <v>707</v>
+      </c>
+      <c r="B329" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D329" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E329" s="11">
+        <v>5</v>
+      </c>
+      <c r="F329" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G329" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H329" s="17">
+        <v>1001209</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8">
+      <c r="A330" s="11" t="s">
+        <v>708</v>
+      </c>
+      <c r="B330" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D330" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E330" s="11">
+        <v>5</v>
+      </c>
+      <c r="F330" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G330" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H330" s="17">
+        <v>1001210</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8">
+      <c r="A331" s="11" t="s">
+        <v>709</v>
+      </c>
+      <c r="B331" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D331" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E331" s="11">
+        <v>5</v>
+      </c>
+      <c r="F331" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G331" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H331" s="17">
+        <v>1001211</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8">
+      <c r="A332" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="B332" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D332" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E332" s="11">
+        <v>8</v>
+      </c>
+      <c r="F332" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G332" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H332" s="17">
+        <v>1001212</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8">
+      <c r="A333" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="B333" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D333" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E333" s="11">
+        <v>2</v>
+      </c>
+      <c r="F333" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G333" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H333" s="17">
+        <v>1001213</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8">
+      <c r="A334" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="B334" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D334" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E334" s="11">
+        <v>8</v>
+      </c>
+      <c r="F334" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G334" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H334" s="17">
+        <v>1001214</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8">
+      <c r="A335" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="B335" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D335" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E335" s="11">
+        <v>6</v>
+      </c>
+      <c r="F335" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G335" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H335" s="17">
+        <v>1001215</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8">
+      <c r="A336" s="11" t="s">
+        <v>713</v>
+      </c>
+      <c r="B336" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D336" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E336" s="11">
+        <v>6</v>
+      </c>
+      <c r="F336" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G336" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H336" s="17">
+        <v>1001216</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8">
+      <c r="A337" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B337" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D337" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E337" s="11">
+        <v>6</v>
+      </c>
+      <c r="F337" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G337" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H337" s="17">
+        <v>1001217</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8">
+      <c r="A338" s="11" t="s">
+        <v>714</v>
+      </c>
+      <c r="B338" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D338" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E338" s="11">
+        <v>4</v>
+      </c>
+      <c r="F338" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G338" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H338" s="17">
+        <v>1001218</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8">
+      <c r="A339" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B339" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D339" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E339" s="11">
+        <v>3</v>
+      </c>
+      <c r="F339" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G339" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H339" s="17">
+        <v>1001219</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8">
+      <c r="A340" s="11" t="s">
+        <v>715</v>
+      </c>
+      <c r="B340" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D340" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E340" s="11">
+        <v>3</v>
+      </c>
+      <c r="F340" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G340" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H340" s="17">
+        <v>1001220</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8">
+      <c r="A341" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="B341" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D341" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E341" s="11">
+        <v>18</v>
+      </c>
+      <c r="F341" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G341" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H341" s="17">
+        <v>1001221</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8">
+      <c r="A342" s="11" t="s">
+        <v>716</v>
+      </c>
+      <c r="B342" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D342" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E342" s="11">
+        <v>5</v>
+      </c>
+      <c r="F342" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G342" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H342" s="17">
+        <v>1001222</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8">
+      <c r="A343" s="11" t="s">
+        <v>717</v>
+      </c>
+      <c r="B343" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D343" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E343" s="11">
+        <v>5</v>
+      </c>
+      <c r="F343" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G343" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H343" s="17">
+        <v>1001223</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8">
+      <c r="A344" s="11" t="s">
+        <v>718</v>
+      </c>
+      <c r="B344" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D344" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E344" s="11">
+        <v>18</v>
+      </c>
+      <c r="F344" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G344" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H344" s="17">
+        <v>1001224</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8">
+      <c r="A345" s="11" t="s">
+        <v>721</v>
+      </c>
+      <c r="B345" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C345" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D345" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E345" s="11">
+        <v>125</v>
+      </c>
+      <c r="F345" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="G345" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H345" s="17">
+        <v>1009032</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="B346" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C346" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D346" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E346" s="11">
+        <v>19.3</v>
+      </c>
+      <c r="F346" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="G346" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H346" s="17">
+        <v>1009033</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8">
+      <c r="A347" s="11" t="s">
+        <v>723</v>
+      </c>
+      <c r="B347" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C347" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D347" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="E347" s="11">
+        <v>12</v>
+      </c>
+      <c r="F347" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G274" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H274" s="16">
-        <v>1006086</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8">
-      <c r="A275" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="B275" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="C275" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D275" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E275" s="9">
-        <v>90</v>
-      </c>
-      <c r="F275" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="G275" s="15" t="s">
-        <v>651</v>
-      </c>
-      <c r="H275" s="10">
-        <v>1001109</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8">
-      <c r="A276" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="B276" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C276" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D276" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E276" s="9">
-        <v>50</v>
-      </c>
-      <c r="F276" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G276" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H276" s="16">
-        <v>1006001</v>
-      </c>
-    </row>
-    <row r="277" spans="1:8">
-      <c r="A277" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="B277" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="C277" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="D277" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="E277" s="9">
-        <v>7.8</v>
-      </c>
-      <c r="F277" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="G277" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="H277" s="16">
-        <v>1009034</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8">
-      <c r="A278" s="17" t="s">
-        <v>654</v>
-      </c>
-      <c r="B278" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="C278" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D278" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="E278" s="9">
-        <v>43.5</v>
-      </c>
-      <c r="F278" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G278" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H278" s="16">
-        <v>1009016</v>
-      </c>
-    </row>
-    <row r="279" spans="1:8">
-      <c r="A279" s="9" t="s">
-        <v>655</v>
-      </c>
-      <c r="B279" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C279" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D279" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E279" s="9">
-        <v>38</v>
-      </c>
-      <c r="F279" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G279" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H279" s="16">
-        <v>1005015</v>
-      </c>
-    </row>
-    <row r="280" spans="1:8">
-      <c r="A280" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="B280" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C280" s="15" t="s">
+      <c r="G347" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H347" s="17">
+        <v>1009040</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8">
+      <c r="A348" s="11" t="s">
+        <v>724</v>
+      </c>
+      <c r="B348" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C348" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D280" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E280" s="9">
-        <v>62</v>
-      </c>
-      <c r="F280" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G280" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H280" s="19" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="281" spans="1:8">
-      <c r="A281" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="B281" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C281" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D281" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E281" s="9">
-        <v>8</v>
-      </c>
-      <c r="F281" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G281" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H281" s="16">
-        <v>1009036</v>
-      </c>
-    </row>
-    <row r="282" spans="1:8">
-      <c r="A282" s="20" t="s">
-        <v>659</v>
-      </c>
-      <c r="B282" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C282" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D282" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E282" s="9">
-        <v>10</v>
-      </c>
-      <c r="F282" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G282" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H282" s="16">
-        <v>1009035</v>
-      </c>
-    </row>
-    <row r="283" spans="1:8">
-      <c r="A283" s="9" t="s">
-        <v>660</v>
-      </c>
-      <c r="B283" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C283" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D283" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E283" s="9">
-        <v>5</v>
-      </c>
-      <c r="F283" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G283" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H283" s="16">
-        <v>1001038</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8">
-      <c r="A284" s="9" t="s">
-        <v>661</v>
-      </c>
-      <c r="B284" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C284" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D284" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E284" s="9">
-        <v>3.5</v>
-      </c>
-      <c r="F284" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G284" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H284" s="16">
-        <v>1001110</v>
-      </c>
-    </row>
-    <row r="285" spans="1:8">
-      <c r="A285" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="B285" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C285" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D285" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E285" s="9">
-        <v>3.5</v>
-      </c>
-      <c r="F285" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G285" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H285" s="16">
-        <v>1001111</v>
-      </c>
-    </row>
-    <row r="286" spans="1:8">
-      <c r="A286" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="B286" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C286" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D286" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E286" s="9">
-        <v>180</v>
-      </c>
-      <c r="F286" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G286" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H286" s="16">
-        <v>1007014</v>
-      </c>
-    </row>
-    <row r="287" spans="1:8">
-      <c r="A287" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="B287" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C287" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D287" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E287" s="9">
-        <v>150</v>
-      </c>
-      <c r="F287" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G287" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H287" s="19" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8">
-      <c r="A288" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="B288" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C288" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D288" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E288" s="9">
-        <v>6.5</v>
-      </c>
-      <c r="F288" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G288" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H288" s="19" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="289" spans="1:8">
-      <c r="A289" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="B289" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C289" s="15" t="s">
+      <c r="D348" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E348" s="11">
+        <v>10</v>
+      </c>
+      <c r="F348" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="G348" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H348" s="17">
+        <v>1003027</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8">
+      <c r="A349" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="B349" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C349" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D289" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E289" s="9">
-        <v>11.5</v>
-      </c>
-      <c r="F289" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G289" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H289" s="16">
-        <v>1003027</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9">
-      <c r="A290" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="B290" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C290" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D290" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E290" s="9">
-        <v>8</v>
-      </c>
-      <c r="F290" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G290" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H290" s="16">
-        <v>1001113</v>
-      </c>
-      <c r="I290" s="16" t="s"/>
-    </row>
-    <row r="291" spans="1:8">
-      <c r="A291" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="B291" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C291" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D291" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E291" s="9">
-        <v>6.5</v>
-      </c>
-      <c r="F291" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G291" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H291" s="16">
-        <v>1001050</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8">
-      <c r="A292" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="B292" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C292" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D292" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E292" s="9">
-        <v>6.5</v>
-      </c>
-      <c r="F292" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G292" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H292" s="16">
-        <v>1001114</v>
-      </c>
-    </row>
-    <row r="293" spans="1:8">
-      <c r="A293" s="9" t="s">
-        <v>672</v>
-      </c>
-      <c r="B293" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C293" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D293" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E293" s="9">
-        <v>5</v>
-      </c>
-      <c r="F293" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G293" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H293" s="16">
-        <v>1001115</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8">
-      <c r="A294" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="B294" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C294" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D294" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E294" s="9">
-        <v>18.5</v>
-      </c>
-      <c r="F294" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G294" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H294" s="16">
-        <v>1003012</v>
-      </c>
-    </row>
-    <row r="295" spans="1:8">
-      <c r="A295" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="B295" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C295" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D295" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E295" s="9">
-        <v>7.5</v>
-      </c>
-      <c r="F295" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G295" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H295" s="16">
-        <v>1002005</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8">
-      <c r="A296" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="B296" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C296" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D296" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E296" s="9">
-        <v>16</v>
-      </c>
-      <c r="F296" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G296" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H296" s="16">
-        <v>1001116</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8">
-      <c r="A297" s="9" t="s">
-        <v>676</v>
-      </c>
-      <c r="B297" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C297" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D297" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E297" s="9">
-        <v>8.6</v>
-      </c>
-      <c r="F297" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G297" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H297" s="19" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8">
-      <c r="A298" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="B298" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C298" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D298" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E298" s="9">
-        <v>20</v>
-      </c>
-      <c r="F298" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G298" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H298" s="16">
-        <v>1001117</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8">
-      <c r="A299" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="B299" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C299" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D299" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E299" s="9">
-        <v>7.5</v>
-      </c>
-      <c r="F299" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G299" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H299" s="16">
-        <v>1001118</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8">
-      <c r="A300" s="9" t="s">
-        <v>679</v>
-      </c>
-      <c r="B300" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C300" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D300" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E300" s="9">
-        <v>32.8</v>
-      </c>
-      <c r="F300" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G300" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H300" s="16">
-        <v>1001119</v>
-      </c>
-    </row>
-    <row r="301" spans="1:8">
-      <c r="A301" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="B301" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C301" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D301" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E301" s="9">
-        <v>4</v>
-      </c>
-      <c r="F301" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G301" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H301" s="16">
-        <v>1001120</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8">
-      <c r="A302" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="B302" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C302" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="D302" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E302" s="9">
-        <v>5</v>
-      </c>
-      <c r="F302" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G302" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H302" s="16">
-        <v>1005005</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8">
-      <c r="A303" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="B303" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C303" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="D303" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E303" s="9">
-        <v>48</v>
-      </c>
-      <c r="F303" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G303" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H303" s="19" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8">
-      <c r="A304" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="B304" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="C304" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="D304" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E304" s="9">
-        <v>27.1</v>
-      </c>
-      <c r="F304" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="G304" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H304" s="16">
-        <v>1006087</v>
-      </c>
-    </row>
-    <row r="305" spans="1:8">
-      <c r="A305" s="9" t="s">
-        <v>685</v>
-      </c>
-      <c r="B305" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C305" s="15" t="s">
-        <v>388</v>
-      </c>
-      <c r="D305" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="E305" s="9">
-        <v>240</v>
-      </c>
-      <c r="F305" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="G305" s="18" t="s">
-        <v>686</v>
-      </c>
-      <c r="H305" s="16">
-        <v>2001060</v>
-      </c>
-    </row>
-    <row r="306" spans="1:8">
-      <c r="A306" s="9" t="s">
-        <v>687</v>
-      </c>
-      <c r="B306" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C306" s="15" t="s">
-        <v>388</v>
-      </c>
-      <c r="D306" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="E306" s="9">
-        <v>98</v>
-      </c>
-      <c r="F306" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="G306" s="18" t="s">
-        <v>686</v>
-      </c>
-      <c r="H306" s="16">
-        <v>2001061</v>
-      </c>
-    </row>
-    <row r="307" spans="1:8">
-      <c r="A307" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="B307" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C307" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="D307" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E307" s="9">
-        <v>26</v>
-      </c>
-      <c r="F307" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="G307" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="H307" s="16">
-        <v>1006088</v>
-      </c>
-    </row>
-    <row r="308" spans="1:8">
-      <c r="A308" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="B308" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C308" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="D308" s="9" t="s"/>
-      <c r="E308" s="9">
-        <v>14.8</v>
-      </c>
-      <c r="F308" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="G308" s="15" t="s">
-        <v>621</v>
-      </c>
-      <c r="H308" s="16">
-        <v>1006089</v>
-      </c>
-    </row>
-    <row r="309" spans="1:8">
-      <c r="A309" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="B309" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C309" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="D309" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E309" s="9">
-        <v>22</v>
-      </c>
-      <c r="F309" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G309" s="15" t="s">
-        <v>621</v>
-      </c>
-      <c r="H309" s="16">
-        <v>1006090</v>
-      </c>
-    </row>
-    <row r="310" spans="1:8">
-      <c r="A310" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="B310" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C310" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="D310" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E310" s="9">
-        <v>48</v>
-      </c>
-      <c r="F310" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="G310" s="15" t="s">
-        <v>621</v>
-      </c>
-      <c r="H310" s="16">
-        <v>1006091</v>
-      </c>
-    </row>
-    <row r="311" spans="1:8">
-      <c r="A311" s="9" t="s">
-        <v>692</v>
-      </c>
-      <c r="B311" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C311" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="D311" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E311" s="9">
-        <v>110</v>
-      </c>
-      <c r="F311" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="G311" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="H311" s="16">
-        <v>1007022</v>
-      </c>
-    </row>
-    <row r="312" spans="1:8">
-      <c r="A312" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="B312" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C312" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="D312" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E312" s="9">
-        <v>68</v>
-      </c>
-      <c r="F312" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="G312" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="H312" s="16">
-        <v>1007023</v>
-      </c>
-    </row>
-    <row r="313" spans="1:8">
-      <c r="A313" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="B313" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C313" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="D313" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E313" s="9">
-        <v>32</v>
-      </c>
-      <c r="F313" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G313" s="15" t="s">
-        <v>621</v>
-      </c>
-      <c r="H313" s="16">
-        <v>1006063</v>
-      </c>
-    </row>
-    <row r="314" spans="1:8">
-      <c r="A314" s="9" t="s">
-        <v>695</v>
-      </c>
-      <c r="B314" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C314" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="D314" s="9" t="s">
-        <v>696</v>
-      </c>
-      <c r="E314" s="9">
-        <v>450</v>
-      </c>
-      <c r="F314" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="G314" s="15" t="s">
-        <v>621</v>
-      </c>
-      <c r="H314" s="16">
-        <v>1006092</v>
-      </c>
-    </row>
-    <row r="315" spans="1:8">
-      <c r="A315" s="9" t="s">
-        <v>698</v>
-      </c>
-      <c r="B315" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="C315" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D315" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="E315" s="9">
-        <v>7.8</v>
-      </c>
-      <c r="F315" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="G315" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="H315" s="16">
-        <v>1009031</v>
-      </c>
-    </row>
-    <row r="316" spans="1:8">
-      <c r="A316" s="9" t="s">
-        <v>699</v>
-      </c>
-      <c r="B316" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C316" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D316" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E316" s="9">
-        <v>14.5</v>
-      </c>
-      <c r="F316" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G316" s="15" t="s">
-        <v>621</v>
-      </c>
-      <c r="H316" s="16">
-        <v>1003005</v>
-      </c>
-    </row>
-    <row r="317" spans="1:8">
-      <c r="A317" s="9" t="s"/>
-      <c r="B317" s="9" t="s"/>
-      <c r="C317" s="15" t="s"/>
-      <c r="D317" s="9" t="s"/>
-      <c r="E317" s="9" t="s"/>
-      <c r="F317" s="9" t="s"/>
-      <c r="G317" s="15" t="s"/>
-      <c r="H317" s="16" t="s"/>
-    </row>
-    <row r="318" spans="1:8">
-      <c r="A318" s="9" t="s"/>
-      <c r="B318" s="9" t="s"/>
-      <c r="C318" s="15" t="s"/>
-      <c r="D318" s="9" t="s"/>
-      <c r="E318" s="9" t="s"/>
-      <c r="F318" s="9" t="s"/>
-      <c r="G318" s="15" t="s"/>
-      <c r="H318" s="16" t="s"/>
-    </row>
-    <row r="319" spans="1:8">
-      <c r="A319" s="9" t="s"/>
-      <c r="B319" s="9" t="s"/>
-      <c r="C319" s="15" t="s"/>
-      <c r="D319" s="9" t="s"/>
-      <c r="E319" s="9" t="s"/>
-      <c r="F319" s="9" t="s"/>
-      <c r="G319" s="15" t="s"/>
-      <c r="H319" s="16" t="s"/>
-    </row>
-    <row r="320" spans="1:8">
-      <c r="A320" s="9" t="s"/>
-      <c r="B320" s="9" t="s"/>
-      <c r="C320" s="15" t="s"/>
-      <c r="D320" s="9" t="s"/>
-      <c r="E320" s="9" t="s"/>
-      <c r="F320" s="9" t="s"/>
-      <c r="G320" s="15" t="s"/>
-      <c r="H320" s="16" t="s"/>
+      <c r="D349" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E349" s="11">
+        <v>54</v>
+      </c>
+      <c r="F349" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="G349" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H349" s="17">
+        <v>1003028</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8">
+      <c r="A350" s="11" t="s"/>
+      <c r="B350" s="11" t="s"/>
+      <c r="C350" s="9" t="s"/>
+      <c r="D350" s="11" t="s"/>
+      <c r="E350" s="11" t="s"/>
+      <c r="F350" s="11" t="s"/>
+      <c r="G350" s="9" t="s"/>
+      <c r="H350" s="17" t="s"/>
+    </row>
+    <row r="351" spans="1:8">
+      <c r="A351" s="11" t="s"/>
+      <c r="B351" s="11" t="s"/>
+      <c r="C351" s="9" t="s"/>
+      <c r="D351" s="11" t="s"/>
+      <c r="E351" s="11" t="s"/>
+      <c r="F351" s="11" t="s"/>
+      <c r="G351" s="9" t="s"/>
+      <c r="H351" s="17" t="s"/>
+    </row>
+    <row r="352" spans="1:8">
+      <c r="A352" s="11" t="s"/>
+      <c r="B352" s="11" t="s"/>
+      <c r="C352" s="9" t="s"/>
+      <c r="D352" s="11" t="s"/>
+      <c r="E352" s="11" t="s"/>
+      <c r="F352" s="11" t="s"/>
+      <c r="G352" s="9" t="s"/>
+      <c r="H352" s="17" t="s"/>
+    </row>
+    <row r="353" spans="1:8">
+      <c r="A353" s="11" t="s"/>
+      <c r="B353" s="11" t="s"/>
+      <c r="C353" s="9" t="s"/>
+      <c r="D353" s="11" t="s"/>
+      <c r="E353" s="11" t="s"/>
+      <c r="F353" s="11" t="s"/>
+      <c r="G353" s="9" t="s"/>
+      <c r="H353" s="17" t="s"/>
+    </row>
+    <row r="354" spans="1:8">
+      <c r="A354" s="11" t="s"/>
+      <c r="B354" s="11" t="s"/>
+      <c r="C354" s="9" t="s"/>
+      <c r="D354" s="11" t="s"/>
+      <c r="E354" s="11" t="s"/>
+      <c r="F354" s="11" t="s"/>
+      <c r="G354" s="9" t="s"/>
+      <c r="H354" s="17" t="s"/>
+    </row>
+    <row r="355" spans="1:8">
+      <c r="A355" s="11" t="s"/>
+      <c r="B355" s="11" t="s"/>
+      <c r="C355" s="9" t="s"/>
+      <c r="D355" s="11" t="s"/>
+      <c r="E355" s="11" t="s"/>
+      <c r="F355" s="11" t="s"/>
+      <c r="G355" s="9" t="s"/>
+      <c r="H355" s="17" t="s"/>
+    </row>
+    <row r="356" spans="1:8">
+      <c r="A356" s="11" t="s"/>
+      <c r="B356" s="11" t="s"/>
+      <c r="C356" s="9" t="s"/>
+      <c r="D356" s="11" t="s"/>
+      <c r="E356" s="11" t="s"/>
+      <c r="F356" s="11" t="s"/>
+      <c r="G356" s="9" t="s"/>
+      <c r="H356" s="17" t="s"/>
+    </row>
+    <row r="357" spans="1:8">
+      <c r="A357" s="11" t="s"/>
+      <c r="B357" s="11" t="s"/>
+      <c r="C357" s="9" t="s"/>
+      <c r="D357" s="11" t="s"/>
+      <c r="E357" s="11" t="s"/>
+      <c r="F357" s="11" t="s"/>
+      <c r="G357" s="9" t="s"/>
+      <c r="H357" s="17" t="s"/>
+    </row>
+    <row r="358" spans="1:8">
+      <c r="A358" s="11" t="s"/>
+      <c r="B358" s="11" t="s"/>
+      <c r="C358" s="9" t="s"/>
+      <c r="D358" s="11" t="s"/>
+      <c r="E358" s="11" t="s"/>
+      <c r="F358" s="11" t="s"/>
+      <c r="G358" s="9" t="s"/>
+      <c r="H358" s="17" t="s"/>
+    </row>
+    <row r="359" spans="1:8">
+      <c r="A359" s="11" t="s"/>
+      <c r="B359" s="11" t="s"/>
+      <c r="C359" s="9" t="s"/>
+      <c r="D359" s="11" t="s"/>
+      <c r="E359" s="11" t="s"/>
+      <c r="F359" s="11" t="s"/>
+      <c r="G359" s="9" t="s"/>
+      <c r="H359" s="17" t="s"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H316">
-    <sortState ref="A2:H316"/>
+  <autoFilter ref="A1:H349">
+    <sortState ref="A2:H349"/>
   </autoFilter>
   <ignoredErrors>
     <ignoredError sqref="B1" numberStoredAsText="1"/>
     <ignoredError sqref="C1" numberStoredAsText="1"/>
     <ignoredError sqref="D1" numberStoredAsText="1"/>
     <ignoredError sqref="E1" numberStoredAsText="1"/>
-    <ignoredError sqref="F1" numberStoredAsText="1"/>
     <ignoredError sqref="G1" numberStoredAsText="1"/>
     <ignoredError sqref="A2" numberStoredAsText="1"/>
     <ignoredError sqref="B2" numberStoredAsText="1"/>
@@ -10984,7 +11977,6 @@
     <ignoredError sqref="H14" numberStoredAsText="1"/>
     <ignoredError sqref="A15" numberStoredAsText="1"/>
     <ignoredError sqref="B15" numberStoredAsText="1"/>
-    <ignoredError sqref="C15" numberStoredAsText="1"/>
     <ignoredError sqref="D15" numberStoredAsText="1"/>
     <ignoredError sqref="E15" numberStoredAsText="1"/>
     <ignoredError sqref="F15" numberStoredAsText="1"/>
@@ -11645,7 +12637,6 @@
     <ignoredError sqref="F100" numberStoredAsText="1"/>
     <ignoredError sqref="G100" numberStoredAsText="1"/>
     <ignoredError sqref="H100" numberStoredAsText="1"/>
-    <ignoredError sqref="A101" numberStoredAsText="1"/>
     <ignoredError sqref="B101" numberStoredAsText="1"/>
     <ignoredError sqref="C101" numberStoredAsText="1"/>
     <ignoredError sqref="D101" numberStoredAsText="1"/>
@@ -11800,7 +12791,6 @@
     <ignoredError sqref="F120" numberStoredAsText="1"/>
     <ignoredError sqref="G120" numberStoredAsText="1"/>
     <ignoredError sqref="H120" numberStoredAsText="1"/>
-    <ignoredError sqref="A121" numberStoredAsText="1"/>
     <ignoredError sqref="B121" numberStoredAsText="1"/>
     <ignoredError sqref="C121" numberStoredAsText="1"/>
     <ignoredError sqref="D121" numberStoredAsText="1"/>
@@ -11809,7 +12799,6 @@
     <ignoredError sqref="G121" numberStoredAsText="1"/>
     <ignoredError sqref="H121" numberStoredAsText="1"/>
     <ignoredError sqref="B122" numberStoredAsText="1"/>
-    <ignoredError sqref="C122" numberStoredAsText="1"/>
     <ignoredError sqref="D122" numberStoredAsText="1"/>
     <ignoredError sqref="E122" numberStoredAsText="1"/>
     <ignoredError sqref="F122" numberStoredAsText="1"/>
@@ -11893,7 +12882,6 @@
     <ignoredError sqref="F133" numberStoredAsText="1"/>
     <ignoredError sqref="G133" numberStoredAsText="1"/>
     <ignoredError sqref="H133" numberStoredAsText="1"/>
-    <ignoredError sqref="A134" numberStoredAsText="1"/>
     <ignoredError sqref="B134" numberStoredAsText="1"/>
     <ignoredError sqref="C134" numberStoredAsText="1"/>
     <ignoredError sqref="D134" numberStoredAsText="1"/>
@@ -11949,7 +12937,6 @@
     <ignoredError sqref="F140" numberStoredAsText="1"/>
     <ignoredError sqref="G140" numberStoredAsText="1"/>
     <ignoredError sqref="H140" numberStoredAsText="1"/>
-    <ignoredError sqref="A141" numberStoredAsText="1"/>
     <ignoredError sqref="B141" numberStoredAsText="1"/>
     <ignoredError sqref="C141" numberStoredAsText="1"/>
     <ignoredError sqref="D141" numberStoredAsText="1"/>
@@ -11977,11 +12964,9 @@
     <ignoredError sqref="B144" numberStoredAsText="1"/>
     <ignoredError sqref="C144" numberStoredAsText="1"/>
     <ignoredError sqref="D144" numberStoredAsText="1"/>
-    <ignoredError sqref="E144" numberStoredAsText="1"/>
     <ignoredError sqref="F144" numberStoredAsText="1"/>
     <ignoredError sqref="G144" numberStoredAsText="1"/>
     <ignoredError sqref="H144" numberStoredAsText="1"/>
-    <ignoredError sqref="A145" numberStoredAsText="1"/>
     <ignoredError sqref="B145" numberStoredAsText="1"/>
     <ignoredError sqref="C145" numberStoredAsText="1"/>
     <ignoredError sqref="D145" numberStoredAsText="1"/>
@@ -12001,7 +12986,6 @@
     <ignoredError sqref="B147" numberStoredAsText="1"/>
     <ignoredError sqref="C147" numberStoredAsText="1"/>
     <ignoredError sqref="D147" numberStoredAsText="1"/>
-    <ignoredError sqref="E147" numberStoredAsText="1"/>
     <ignoredError sqref="F147" numberStoredAsText="1"/>
     <ignoredError sqref="G147" numberStoredAsText="1"/>
     <ignoredError sqref="H147" numberStoredAsText="1"/>
@@ -12036,10 +13020,8 @@
     <ignoredError sqref="F151" numberStoredAsText="1"/>
     <ignoredError sqref="G151" numberStoredAsText="1"/>
     <ignoredError sqref="H151" numberStoredAsText="1"/>
-    <ignoredError sqref="A152" numberStoredAsText="1"/>
     <ignoredError sqref="B152" numberStoredAsText="1"/>
     <ignoredError sqref="C152" numberStoredAsText="1"/>
-    <ignoredError sqref="D152" numberStoredAsText="1"/>
     <ignoredError sqref="E152" numberStoredAsText="1"/>
     <ignoredError sqref="F152" numberStoredAsText="1"/>
     <ignoredError sqref="G152" numberStoredAsText="1"/>
@@ -12071,7 +13053,6 @@
     <ignoredError sqref="B156" numberStoredAsText="1"/>
     <ignoredError sqref="C156" numberStoredAsText="1"/>
     <ignoredError sqref="D156" numberStoredAsText="1"/>
-    <ignoredError sqref="E156" numberStoredAsText="1"/>
     <ignoredError sqref="F156" numberStoredAsText="1"/>
     <ignoredError sqref="G156" numberStoredAsText="1"/>
     <ignoredError sqref="H156" numberStoredAsText="1"/>
@@ -12079,7 +13060,6 @@
     <ignoredError sqref="B157" numberStoredAsText="1"/>
     <ignoredError sqref="C157" numberStoredAsText="1"/>
     <ignoredError sqref="D157" numberStoredAsText="1"/>
-    <ignoredError sqref="E157" numberStoredAsText="1"/>
     <ignoredError sqref="F157" numberStoredAsText="1"/>
     <ignoredError sqref="G157" numberStoredAsText="1"/>
     <ignoredError sqref="H157" numberStoredAsText="1"/>
@@ -12103,7 +13083,6 @@
     <ignoredError sqref="B160" numberStoredAsText="1"/>
     <ignoredError sqref="C160" numberStoredAsText="1"/>
     <ignoredError sqref="D160" numberStoredAsText="1"/>
-    <ignoredError sqref="E160" numberStoredAsText="1"/>
     <ignoredError sqref="F160" numberStoredAsText="1"/>
     <ignoredError sqref="G160" numberStoredAsText="1"/>
     <ignoredError sqref="H160" numberStoredAsText="1"/>
@@ -12111,7 +13090,6 @@
     <ignoredError sqref="B161" numberStoredAsText="1"/>
     <ignoredError sqref="C161" numberStoredAsText="1"/>
     <ignoredError sqref="D161" numberStoredAsText="1"/>
-    <ignoredError sqref="E161" numberStoredAsText="1"/>
     <ignoredError sqref="F161" numberStoredAsText="1"/>
     <ignoredError sqref="G161" numberStoredAsText="1"/>
     <ignoredError sqref="H161" numberStoredAsText="1"/>
@@ -12174,7 +13152,6 @@
     <ignoredError sqref="B169" numberStoredAsText="1"/>
     <ignoredError sqref="C169" numberStoredAsText="1"/>
     <ignoredError sqref="D169" numberStoredAsText="1"/>
-    <ignoredError sqref="E169" numberStoredAsText="1"/>
     <ignoredError sqref="F169" numberStoredAsText="1"/>
     <ignoredError sqref="G169" numberStoredAsText="1"/>
     <ignoredError sqref="H169" numberStoredAsText="1"/>
@@ -12188,7 +13165,6 @@
     <ignoredError sqref="H170" numberStoredAsText="1"/>
     <ignoredError sqref="A171" numberStoredAsText="1"/>
     <ignoredError sqref="B171" numberStoredAsText="1"/>
-    <ignoredError sqref="C171" numberStoredAsText="1"/>
     <ignoredError sqref="D171" numberStoredAsText="1"/>
     <ignoredError sqref="E171" numberStoredAsText="1"/>
     <ignoredError sqref="F171" numberStoredAsText="1"/>
@@ -12212,7 +13188,6 @@
     <ignoredError sqref="H173" numberStoredAsText="1"/>
     <ignoredError sqref="A174" numberStoredAsText="1"/>
     <ignoredError sqref="B174" numberStoredAsText="1"/>
-    <ignoredError sqref="C174" numberStoredAsText="1"/>
     <ignoredError sqref="D174" numberStoredAsText="1"/>
     <ignoredError sqref="E174" numberStoredAsText="1"/>
     <ignoredError sqref="F174" numberStoredAsText="1"/>
@@ -12220,7 +13195,6 @@
     <ignoredError sqref="H174" numberStoredAsText="1"/>
     <ignoredError sqref="A175" numberStoredAsText="1"/>
     <ignoredError sqref="B175" numberStoredAsText="1"/>
-    <ignoredError sqref="C175" numberStoredAsText="1"/>
     <ignoredError sqref="D175" numberStoredAsText="1"/>
     <ignoredError sqref="E175" numberStoredAsText="1"/>
     <ignoredError sqref="F175" numberStoredAsText="1"/>
@@ -12236,7 +13210,6 @@
     <ignoredError sqref="H176" numberStoredAsText="1"/>
     <ignoredError sqref="A177" numberStoredAsText="1"/>
     <ignoredError sqref="B177" numberStoredAsText="1"/>
-    <ignoredError sqref="C177" numberStoredAsText="1"/>
     <ignoredError sqref="D177" numberStoredAsText="1"/>
     <ignoredError sqref="E177" numberStoredAsText="1"/>
     <ignoredError sqref="F177" numberStoredAsText="1"/>
@@ -12244,7 +13217,6 @@
     <ignoredError sqref="H177" numberStoredAsText="1"/>
     <ignoredError sqref="A178" numberStoredAsText="1"/>
     <ignoredError sqref="B178" numberStoredAsText="1"/>
-    <ignoredError sqref="C178" numberStoredAsText="1"/>
     <ignoredError sqref="D178" numberStoredAsText="1"/>
     <ignoredError sqref="E178" numberStoredAsText="1"/>
     <ignoredError sqref="F178" numberStoredAsText="1"/>
@@ -12259,7 +13231,6 @@
     <ignoredError sqref="H179" numberStoredAsText="1"/>
     <ignoredError sqref="A180" numberStoredAsText="1"/>
     <ignoredError sqref="B180" numberStoredAsText="1"/>
-    <ignoredError sqref="C180" numberStoredAsText="1"/>
     <ignoredError sqref="D180" numberStoredAsText="1"/>
     <ignoredError sqref="E180" numberStoredAsText="1"/>
     <ignoredError sqref="F180" numberStoredAsText="1"/>
@@ -12267,7 +13238,6 @@
     <ignoredError sqref="H180" numberStoredAsText="1"/>
     <ignoredError sqref="A181" numberStoredAsText="1"/>
     <ignoredError sqref="B181" numberStoredAsText="1"/>
-    <ignoredError sqref="C181" numberStoredAsText="1"/>
     <ignoredError sqref="D181" numberStoredAsText="1"/>
     <ignoredError sqref="E181" numberStoredAsText="1"/>
     <ignoredError sqref="F181" numberStoredAsText="1"/>
@@ -12283,7 +13253,6 @@
     <ignoredError sqref="H182" numberStoredAsText="1"/>
     <ignoredError sqref="A183" numberStoredAsText="1"/>
     <ignoredError sqref="B183" numberStoredAsText="1"/>
-    <ignoredError sqref="C183" numberStoredAsText="1"/>
     <ignoredError sqref="D183" numberStoredAsText="1"/>
     <ignoredError sqref="E183" numberStoredAsText="1"/>
     <ignoredError sqref="F183" numberStoredAsText="1"/>
@@ -12291,7 +13260,6 @@
     <ignoredError sqref="H183" numberStoredAsText="1"/>
     <ignoredError sqref="A184" numberStoredAsText="1"/>
     <ignoredError sqref="B184" numberStoredAsText="1"/>
-    <ignoredError sqref="C184" numberStoredAsText="1"/>
     <ignoredError sqref="D184" numberStoredAsText="1"/>
     <ignoredError sqref="E184" numberStoredAsText="1"/>
     <ignoredError sqref="F184" numberStoredAsText="1"/>
@@ -12299,7 +13267,6 @@
     <ignoredError sqref="H184" numberStoredAsText="1"/>
     <ignoredError sqref="A185" numberStoredAsText="1"/>
     <ignoredError sqref="B185" numberStoredAsText="1"/>
-    <ignoredError sqref="C185" numberStoredAsText="1"/>
     <ignoredError sqref="D185" numberStoredAsText="1"/>
     <ignoredError sqref="E185" numberStoredAsText="1"/>
     <ignoredError sqref="F185" numberStoredAsText="1"/>
@@ -12307,7 +13274,6 @@
     <ignoredError sqref="H185" numberStoredAsText="1"/>
     <ignoredError sqref="A186" numberStoredAsText="1"/>
     <ignoredError sqref="B186" numberStoredAsText="1"/>
-    <ignoredError sqref="C186" numberStoredAsText="1"/>
     <ignoredError sqref="D186" numberStoredAsText="1"/>
     <ignoredError sqref="E186" numberStoredAsText="1"/>
     <ignoredError sqref="F186" numberStoredAsText="1"/>
@@ -12315,7 +13281,6 @@
     <ignoredError sqref="H186" numberStoredAsText="1"/>
     <ignoredError sqref="A187" numberStoredAsText="1"/>
     <ignoredError sqref="B187" numberStoredAsText="1"/>
-    <ignoredError sqref="C187" numberStoredAsText="1"/>
     <ignoredError sqref="D187" numberStoredAsText="1"/>
     <ignoredError sqref="E187" numberStoredAsText="1"/>
     <ignoredError sqref="F187" numberStoredAsText="1"/>
@@ -12323,7 +13288,6 @@
     <ignoredError sqref="H187" numberStoredAsText="1"/>
     <ignoredError sqref="A188" numberStoredAsText="1"/>
     <ignoredError sqref="B188" numberStoredAsText="1"/>
-    <ignoredError sqref="C188" numberStoredAsText="1"/>
     <ignoredError sqref="D188" numberStoredAsText="1"/>
     <ignoredError sqref="E188" numberStoredAsText="1"/>
     <ignoredError sqref="F188" numberStoredAsText="1"/>
@@ -12331,7 +13295,6 @@
     <ignoredError sqref="H188" numberStoredAsText="1"/>
     <ignoredError sqref="A189" numberStoredAsText="1"/>
     <ignoredError sqref="B189" numberStoredAsText="1"/>
-    <ignoredError sqref="C189" numberStoredAsText="1"/>
     <ignoredError sqref="D189" numberStoredAsText="1"/>
     <ignoredError sqref="E189" numberStoredAsText="1"/>
     <ignoredError sqref="F189" numberStoredAsText="1"/>
@@ -12339,7 +13302,6 @@
     <ignoredError sqref="H189" numberStoredAsText="1"/>
     <ignoredError sqref="A190" numberStoredAsText="1"/>
     <ignoredError sqref="B190" numberStoredAsText="1"/>
-    <ignoredError sqref="C190" numberStoredAsText="1"/>
     <ignoredError sqref="D190" numberStoredAsText="1"/>
     <ignoredError sqref="E190" numberStoredAsText="1"/>
     <ignoredError sqref="F190" numberStoredAsText="1"/>
@@ -12347,7 +13309,6 @@
     <ignoredError sqref="H190" numberStoredAsText="1"/>
     <ignoredError sqref="A191" numberStoredAsText="1"/>
     <ignoredError sqref="B191" numberStoredAsText="1"/>
-    <ignoredError sqref="C191" numberStoredAsText="1"/>
     <ignoredError sqref="D191" numberStoredAsText="1"/>
     <ignoredError sqref="E191" numberStoredAsText="1"/>
     <ignoredError sqref="F191" numberStoredAsText="1"/>
@@ -12355,7 +13316,6 @@
     <ignoredError sqref="H191" numberStoredAsText="1"/>
     <ignoredError sqref="A192" numberStoredAsText="1"/>
     <ignoredError sqref="B192" numberStoredAsText="1"/>
-    <ignoredError sqref="C192" numberStoredAsText="1"/>
     <ignoredError sqref="D192" numberStoredAsText="1"/>
     <ignoredError sqref="E192" numberStoredAsText="1"/>
     <ignoredError sqref="F192" numberStoredAsText="1"/>
@@ -12363,7 +13323,6 @@
     <ignoredError sqref="H192" numberStoredAsText="1"/>
     <ignoredError sqref="A193" numberStoredAsText="1"/>
     <ignoredError sqref="B193" numberStoredAsText="1"/>
-    <ignoredError sqref="C193" numberStoredAsText="1"/>
     <ignoredError sqref="D193" numberStoredAsText="1"/>
     <ignoredError sqref="E193" numberStoredAsText="1"/>
     <ignoredError sqref="F193" numberStoredAsText="1"/>
@@ -12371,14 +13330,12 @@
     <ignoredError sqref="H193" numberStoredAsText="1"/>
     <ignoredError sqref="A194" numberStoredAsText="1"/>
     <ignoredError sqref="B194" numberStoredAsText="1"/>
-    <ignoredError sqref="C194" numberStoredAsText="1"/>
     <ignoredError sqref="D194" numberStoredAsText="1"/>
     <ignoredError sqref="E194" numberStoredAsText="1"/>
     <ignoredError sqref="F194" numberStoredAsText="1"/>
     <ignoredError sqref="G194" numberStoredAsText="1"/>
     <ignoredError sqref="A195" numberStoredAsText="1"/>
     <ignoredError sqref="B195" numberStoredAsText="1"/>
-    <ignoredError sqref="C195" numberStoredAsText="1"/>
     <ignoredError sqref="D195" numberStoredAsText="1"/>
     <ignoredError sqref="E195" numberStoredAsText="1"/>
     <ignoredError sqref="F195" numberStoredAsText="1"/>
@@ -12386,7 +13343,6 @@
     <ignoredError sqref="H195" numberStoredAsText="1"/>
     <ignoredError sqref="A196" numberStoredAsText="1"/>
     <ignoredError sqref="B196" numberStoredAsText="1"/>
-    <ignoredError sqref="C196" numberStoredAsText="1"/>
     <ignoredError sqref="D196" numberStoredAsText="1"/>
     <ignoredError sqref="E196" numberStoredAsText="1"/>
     <ignoredError sqref="F196" numberStoredAsText="1"/>
@@ -12394,7 +13350,6 @@
     <ignoredError sqref="H196" numberStoredAsText="1"/>
     <ignoredError sqref="A197" numberStoredAsText="1"/>
     <ignoredError sqref="B197" numberStoredAsText="1"/>
-    <ignoredError sqref="C197" numberStoredAsText="1"/>
     <ignoredError sqref="D197" numberStoredAsText="1"/>
     <ignoredError sqref="E197" numberStoredAsText="1"/>
     <ignoredError sqref="F197" numberStoredAsText="1"/>
@@ -12402,7 +13357,6 @@
     <ignoredError sqref="H197" numberStoredAsText="1"/>
     <ignoredError sqref="A198" numberStoredAsText="1"/>
     <ignoredError sqref="B198" numberStoredAsText="1"/>
-    <ignoredError sqref="C198" numberStoredAsText="1"/>
     <ignoredError sqref="D198" numberStoredAsText="1"/>
     <ignoredError sqref="E198" numberStoredAsText="1"/>
     <ignoredError sqref="F198" numberStoredAsText="1"/>
@@ -12410,7 +13364,6 @@
     <ignoredError sqref="H198" numberStoredAsText="1"/>
     <ignoredError sqref="A199" numberStoredAsText="1"/>
     <ignoredError sqref="B199" numberStoredAsText="1"/>
-    <ignoredError sqref="C199" numberStoredAsText="1"/>
     <ignoredError sqref="D199" numberStoredAsText="1"/>
     <ignoredError sqref="E199" numberStoredAsText="1"/>
     <ignoredError sqref="F199" numberStoredAsText="1"/>
@@ -12418,7 +13371,6 @@
     <ignoredError sqref="H199" numberStoredAsText="1"/>
     <ignoredError sqref="A200" numberStoredAsText="1"/>
     <ignoredError sqref="B200" numberStoredAsText="1"/>
-    <ignoredError sqref="C200" numberStoredAsText="1"/>
     <ignoredError sqref="D200" numberStoredAsText="1"/>
     <ignoredError sqref="E200" numberStoredAsText="1"/>
     <ignoredError sqref="F200" numberStoredAsText="1"/>
@@ -12426,7 +13378,6 @@
     <ignoredError sqref="H200" numberStoredAsText="1"/>
     <ignoredError sqref="A201" numberStoredAsText="1"/>
     <ignoredError sqref="B201" numberStoredAsText="1"/>
-    <ignoredError sqref="C201" numberStoredAsText="1"/>
     <ignoredError sqref="D201" numberStoredAsText="1"/>
     <ignoredError sqref="E201" numberStoredAsText="1"/>
     <ignoredError sqref="F201" numberStoredAsText="1"/>
@@ -12434,7 +13385,6 @@
     <ignoredError sqref="H201" numberStoredAsText="1"/>
     <ignoredError sqref="A202" numberStoredAsText="1"/>
     <ignoredError sqref="B202" numberStoredAsText="1"/>
-    <ignoredError sqref="C202" numberStoredAsText="1"/>
     <ignoredError sqref="D202" numberStoredAsText="1"/>
     <ignoredError sqref="E202" numberStoredAsText="1"/>
     <ignoredError sqref="F202" numberStoredAsText="1"/>
@@ -12442,7 +13392,6 @@
     <ignoredError sqref="H202" numberStoredAsText="1"/>
     <ignoredError sqref="A203" numberStoredAsText="1"/>
     <ignoredError sqref="B203" numberStoredAsText="1"/>
-    <ignoredError sqref="C203" numberStoredAsText="1"/>
     <ignoredError sqref="D203" numberStoredAsText="1"/>
     <ignoredError sqref="E203" numberStoredAsText="1"/>
     <ignoredError sqref="F203" numberStoredAsText="1"/>
@@ -12450,7 +13399,6 @@
     <ignoredError sqref="H203" numberStoredAsText="1"/>
     <ignoredError sqref="A204" numberStoredAsText="1"/>
     <ignoredError sqref="B204" numberStoredAsText="1"/>
-    <ignoredError sqref="C204" numberStoredAsText="1"/>
     <ignoredError sqref="D204" numberStoredAsText="1"/>
     <ignoredError sqref="E204" numberStoredAsText="1"/>
     <ignoredError sqref="F204" numberStoredAsText="1"/>
@@ -12458,7 +13406,6 @@
     <ignoredError sqref="H204" numberStoredAsText="1"/>
     <ignoredError sqref="A205" numberStoredAsText="1"/>
     <ignoredError sqref="B205" numberStoredAsText="1"/>
-    <ignoredError sqref="C205" numberStoredAsText="1"/>
     <ignoredError sqref="D205" numberStoredAsText="1"/>
     <ignoredError sqref="E205" numberStoredAsText="1"/>
     <ignoredError sqref="F205" numberStoredAsText="1"/>
@@ -12466,7 +13413,6 @@
     <ignoredError sqref="H205" numberStoredAsText="1"/>
     <ignoredError sqref="A206" numberStoredAsText="1"/>
     <ignoredError sqref="B206" numberStoredAsText="1"/>
-    <ignoredError sqref="C206" numberStoredAsText="1"/>
     <ignoredError sqref="D206" numberStoredAsText="1"/>
     <ignoredError sqref="E206" numberStoredAsText="1"/>
     <ignoredError sqref="F206" numberStoredAsText="1"/>
@@ -12474,7 +13420,6 @@
     <ignoredError sqref="H206" numberStoredAsText="1"/>
     <ignoredError sqref="A207" numberStoredAsText="1"/>
     <ignoredError sqref="B207" numberStoredAsText="1"/>
-    <ignoredError sqref="C207" numberStoredAsText="1"/>
     <ignoredError sqref="D207" numberStoredAsText="1"/>
     <ignoredError sqref="E207" numberStoredAsText="1"/>
     <ignoredError sqref="F207" numberStoredAsText="1"/>
@@ -12490,7 +13435,6 @@
     <ignoredError sqref="H208" numberStoredAsText="1"/>
     <ignoredError sqref="A209" numberStoredAsText="1"/>
     <ignoredError sqref="B209" numberStoredAsText="1"/>
-    <ignoredError sqref="C209" numberStoredAsText="1"/>
     <ignoredError sqref="D209" numberStoredAsText="1"/>
     <ignoredError sqref="E209" numberStoredAsText="1"/>
     <ignoredError sqref="F209" numberStoredAsText="1"/>
@@ -12498,7 +13442,6 @@
     <ignoredError sqref="H209" numberStoredAsText="1"/>
     <ignoredError sqref="A210" numberStoredAsText="1"/>
     <ignoredError sqref="B210" numberStoredAsText="1"/>
-    <ignoredError sqref="C210" numberStoredAsText="1"/>
     <ignoredError sqref="D210" numberStoredAsText="1"/>
     <ignoredError sqref="E210" numberStoredAsText="1"/>
     <ignoredError sqref="F210" numberStoredAsText="1"/>
@@ -12506,7 +13449,6 @@
     <ignoredError sqref="H210" numberStoredAsText="1"/>
     <ignoredError sqref="A211" numberStoredAsText="1"/>
     <ignoredError sqref="B211" numberStoredAsText="1"/>
-    <ignoredError sqref="C211" numberStoredAsText="1"/>
     <ignoredError sqref="D211" numberStoredAsText="1"/>
     <ignoredError sqref="E211" numberStoredAsText="1"/>
     <ignoredError sqref="F211" numberStoredAsText="1"/>
@@ -12514,7 +13456,6 @@
     <ignoredError sqref="H211" numberStoredAsText="1"/>
     <ignoredError sqref="A212" numberStoredAsText="1"/>
     <ignoredError sqref="B212" numberStoredAsText="1"/>
-    <ignoredError sqref="C212" numberStoredAsText="1"/>
     <ignoredError sqref="D212" numberStoredAsText="1"/>
     <ignoredError sqref="E212" numberStoredAsText="1"/>
     <ignoredError sqref="F212" numberStoredAsText="1"/>
@@ -12530,7 +13471,6 @@
     <ignoredError sqref="H213" numberStoredAsText="1"/>
     <ignoredError sqref="A214" numberStoredAsText="1"/>
     <ignoredError sqref="B214" numberStoredAsText="1"/>
-    <ignoredError sqref="C214" numberStoredAsText="1"/>
     <ignoredError sqref="D214" numberStoredAsText="1"/>
     <ignoredError sqref="E214" numberStoredAsText="1"/>
     <ignoredError sqref="F214" numberStoredAsText="1"/>
@@ -12538,7 +13478,6 @@
     <ignoredError sqref="H214" numberStoredAsText="1"/>
     <ignoredError sqref="A215" numberStoredAsText="1"/>
     <ignoredError sqref="B215" numberStoredAsText="1"/>
-    <ignoredError sqref="C215" numberStoredAsText="1"/>
     <ignoredError sqref="D215" numberStoredAsText="1"/>
     <ignoredError sqref="E215" numberStoredAsText="1"/>
     <ignoredError sqref="F215" numberStoredAsText="1"/>
@@ -12546,7 +13485,6 @@
     <ignoredError sqref="H215" numberStoredAsText="1"/>
     <ignoredError sqref="A216" numberStoredAsText="1"/>
     <ignoredError sqref="B216" numberStoredAsText="1"/>
-    <ignoredError sqref="C216" numberStoredAsText="1"/>
     <ignoredError sqref="D216" numberStoredAsText="1"/>
     <ignoredError sqref="E216" numberStoredAsText="1"/>
     <ignoredError sqref="F216" numberStoredAsText="1"/>
@@ -12554,7 +13492,6 @@
     <ignoredError sqref="H216" numberStoredAsText="1"/>
     <ignoredError sqref="A217" numberStoredAsText="1"/>
     <ignoredError sqref="B217" numberStoredAsText="1"/>
-    <ignoredError sqref="C217" numberStoredAsText="1"/>
     <ignoredError sqref="D217" numberStoredAsText="1"/>
     <ignoredError sqref="E217" numberStoredAsText="1"/>
     <ignoredError sqref="F217" numberStoredAsText="1"/>
@@ -12611,7 +13548,6 @@
     <ignoredError sqref="B224" numberStoredAsText="1"/>
     <ignoredError sqref="C224" numberStoredAsText="1"/>
     <ignoredError sqref="D224" numberStoredAsText="1"/>
-    <ignoredError sqref="E224" numberStoredAsText="1"/>
     <ignoredError sqref="F224" numberStoredAsText="1"/>
     <ignoredError sqref="G224" numberStoredAsText="1"/>
     <ignoredError sqref="H224" numberStoredAsText="1"/>
@@ -12631,7 +13567,6 @@
     <ignoredError sqref="F226" numberStoredAsText="1"/>
     <ignoredError sqref="G226" numberStoredAsText="1"/>
     <ignoredError sqref="H226" numberStoredAsText="1"/>
-    <ignoredError sqref="A227" numberStoredAsText="1"/>
     <ignoredError sqref="B227" numberStoredAsText="1"/>
     <ignoredError sqref="C227" numberStoredAsText="1"/>
     <ignoredError sqref="D227" numberStoredAsText="1"/>
@@ -12656,10 +13591,7 @@
     <ignoredError sqref="G229" numberStoredAsText="1"/>
     <ignoredError sqref="H229" numberStoredAsText="1"/>
     <ignoredError sqref="A230" numberStoredAsText="1"/>
-    <ignoredError sqref="B230" numberStoredAsText="1"/>
     <ignoredError sqref="C230" numberStoredAsText="1"/>
-    <ignoredError sqref="D230" numberStoredAsText="1"/>
-    <ignoredError sqref="E230" numberStoredAsText="1"/>
     <ignoredError sqref="F230" numberStoredAsText="1"/>
     <ignoredError sqref="G230" numberStoredAsText="1"/>
     <ignoredError sqref="H230" numberStoredAsText="1"/>
@@ -12675,7 +13607,6 @@
     <ignoredError sqref="B232" numberStoredAsText="1"/>
     <ignoredError sqref="C232" numberStoredAsText="1"/>
     <ignoredError sqref="D232" numberStoredAsText="1"/>
-    <ignoredError sqref="E232" numberStoredAsText="1"/>
     <ignoredError sqref="F232" numberStoredAsText="1"/>
     <ignoredError sqref="G232" numberStoredAsText="1"/>
     <ignoredError sqref="H232" numberStoredAsText="1"/>
@@ -12683,7 +13614,6 @@
     <ignoredError sqref="B233" numberStoredAsText="1"/>
     <ignoredError sqref="C233" numberStoredAsText="1"/>
     <ignoredError sqref="D233" numberStoredAsText="1"/>
-    <ignoredError sqref="E233" numberStoredAsText="1"/>
     <ignoredError sqref="F233" numberStoredAsText="1"/>
     <ignoredError sqref="G233" numberStoredAsText="1"/>
     <ignoredError sqref="H233" numberStoredAsText="1"/>
@@ -12725,7 +13655,6 @@
     <ignoredError sqref="E238" numberStoredAsText="1"/>
     <ignoredError sqref="F238" numberStoredAsText="1"/>
     <ignoredError sqref="G238" numberStoredAsText="1"/>
-    <ignoredError sqref="H238" numberStoredAsText="1"/>
     <ignoredError sqref="A239" numberStoredAsText="1"/>
     <ignoredError sqref="B239" numberStoredAsText="1"/>
     <ignoredError sqref="C239" numberStoredAsText="1"/>
@@ -12813,7 +13742,6 @@
     <ignoredError sqref="H249" numberStoredAsText="1"/>
     <ignoredError sqref="A250" numberStoredAsText="1"/>
     <ignoredError sqref="B250" numberStoredAsText="1"/>
-    <ignoredError sqref="C250" numberStoredAsText="1"/>
     <ignoredError sqref="D250" numberStoredAsText="1"/>
     <ignoredError sqref="E250" numberStoredAsText="1"/>
     <ignoredError sqref="F250" numberStoredAsText="1"/>
@@ -12821,7 +13749,6 @@
     <ignoredError sqref="H250" numberStoredAsText="1"/>
     <ignoredError sqref="A251" numberStoredAsText="1"/>
     <ignoredError sqref="B251" numberStoredAsText="1"/>
-    <ignoredError sqref="C251" numberStoredAsText="1"/>
     <ignoredError sqref="D251" numberStoredAsText="1"/>
     <ignoredError sqref="E251" numberStoredAsText="1"/>
     <ignoredError sqref="F251" numberStoredAsText="1"/>
@@ -12829,7 +13756,6 @@
     <ignoredError sqref="H251" numberStoredAsText="1"/>
     <ignoredError sqref="A252" numberStoredAsText="1"/>
     <ignoredError sqref="B252" numberStoredAsText="1"/>
-    <ignoredError sqref="C252" numberStoredAsText="1"/>
     <ignoredError sqref="D252" numberStoredAsText="1"/>
     <ignoredError sqref="E252" numberStoredAsText="1"/>
     <ignoredError sqref="F252" numberStoredAsText="1"/>
@@ -12913,80 +13839,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="21" t="s">
+      <c r="F1" s="22" t="s">
+        <v>719</v>
+      </c>
+      <c r="G1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="22">
+      <c r="B2" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="23">
         <v>17.5</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="22" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="23" t="s">
-        <v>700</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="24" t="s">
+        <v>720</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="23">
         <v>115</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="22" t="s">
         <v>22</v>
       </c>
     </row>

--- a/excel/云下/云下物料.xlsx
+++ b/excel/云下/云下物料.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="722">
   <si>
     <t/>
   </si>
@@ -34,7 +34,7 @@
     <t>价格</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>供应商</t>
   </si>
   <si>
     <t>档口</t>
@@ -853,10 +853,10 @@
     <t>1006055</t>
   </si>
   <si>
-    <t>厨邦酱油</t>
-  </si>
-  <si>
-    <t>16.8</t>
+    <t>厨邦特级生抽</t>
+  </si>
+  <si>
+    <t>820ml</t>
   </si>
   <si>
     <t>1006014</t>
@@ -865,7 +865,7 @@
     <t>东古一品鲜酱油</t>
   </si>
   <si>
-    <t>7.85</t>
+    <t>500ml</t>
   </si>
   <si>
     <t>1006041</t>
@@ -895,7 +895,7 @@
     <t>蚝油</t>
   </si>
   <si>
-    <t>33.7</t>
+    <t>6000g</t>
   </si>
   <si>
     <t>1006030</t>
@@ -904,7 +904,7 @@
     <t>胡椒粉</t>
   </si>
   <si>
-    <t>138.6</t>
+    <t>510g</t>
   </si>
   <si>
     <t>1006080</t>
@@ -1009,9 +1009,6 @@
     <t>400g</t>
   </si>
   <si>
-    <t>1.18</t>
-  </si>
-  <si>
     <t>1006022</t>
   </si>
   <si>
@@ -1099,7 +1096,7 @@
     <t>十月稻田香米</t>
   </si>
   <si>
-    <t>1箱=6袋 1袋=3000g</t>
+    <t>1箱=8袋 1袋=3500g</t>
   </si>
   <si>
     <t>276</t>
@@ -1522,9 +1519,6 @@
     <t>云南白酒</t>
   </si>
   <si>
-    <t>酒类</t>
-  </si>
-  <si>
     <t>10kg</t>
   </si>
   <si>
@@ -1588,9 +1582,6 @@
     <t>鲈鱼</t>
   </si>
   <si>
-    <t>海鲜类</t>
-  </si>
-  <si>
     <t>咸蛋黄</t>
   </si>
   <si>
@@ -1609,9 +1600,6 @@
     <t>面条</t>
   </si>
   <si>
-    <t>粮油类</t>
-  </si>
-  <si>
     <t>豇豆</t>
   </si>
   <si>
@@ -1639,6 +1627,9 @@
     <t>味精</t>
   </si>
   <si>
+    <t>2000g</t>
+  </si>
+  <si>
     <t>鱿鱼</t>
   </si>
   <si>
@@ -1732,6 +1723,9 @@
     <t>加长胶皮手套</t>
   </si>
   <si>
+    <t>双</t>
+  </si>
+  <si>
     <t>1双</t>
   </si>
   <si>
@@ -1816,9 +1810,6 @@
     <t>72度葡萄烈酒</t>
   </si>
   <si>
-    <t>500ml</t>
-  </si>
-  <si>
     <t>自采</t>
   </si>
   <si>
@@ -1868,6 +1859,9 @@
   </si>
   <si>
     <t>马苏碎</t>
+  </si>
+  <si>
+    <t>3500g</t>
   </si>
   <si>
     <t>福运顺通（北京）贸易有限公司</t>
@@ -1955,9 +1949,6 @@
     <t>香菜籽粉</t>
   </si>
   <si>
-    <t>伯爵红茶巴斯克</t>
-  </si>
-  <si>
     <t>乳饼</t>
   </si>
   <si>
@@ -2181,28 +2172,22 @@
     <t>贡菜干</t>
   </si>
   <si>
-    <t>供应商</t>
+    <t>雪川土豆块</t>
+  </si>
+  <si>
+    <t>半切带皮土豆</t>
+  </si>
+  <si>
+    <t>傣家白酸笋</t>
+  </si>
+  <si>
+    <t>猪里脊</t>
+  </si>
+  <si>
+    <t>牛肉</t>
   </si>
   <si>
     <t>包浆豆腐1</t>
-  </si>
-  <si>
-    <t>雪川土豆块</t>
-  </si>
-  <si>
-    <t>半切带皮土豆</t>
-  </si>
-  <si>
-    <t>傣家白酸笋</t>
-  </si>
-  <si>
-    <t>猪里脊</t>
-  </si>
-  <si>
-    <t>牛肉</t>
-  </si>
-  <si>
-    <t>双</t>
   </si>
 </sst>
 </file>
@@ -2293,7 +2278,7 @@
   <cellStyleXfs>
     <xf numFmtId="300" fontId="11" fillId="3" borderId="1" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2349,6 +2334,9 @@
     <xf numFmtId="300" fontId="11" fillId="3" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf fontId="3" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
     <xf fontId="10" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles>
@@ -2705,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>7</v>
@@ -3078,7 +3066,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="25" customFormat="1">
+    <row r="16" spans="1:8" s="26" customFormat="1">
       <c r="A16" s="8" t="s">
         <v>70</v>
       </c>
@@ -3484,8 +3472,8 @@
       <c r="E31" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>127</v>
+      <c r="F31" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>32</v>
@@ -3510,8 +3498,8 @@
       <c r="E32" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>127</v>
+      <c r="F32" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>32</v>
@@ -3536,8 +3524,8 @@
       <c r="E33" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>127</v>
+      <c r="F33" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>32</v>
@@ -3562,8 +3550,8 @@
       <c r="E34" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>127</v>
+      <c r="F34" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>32</v>
@@ -3588,8 +3576,8 @@
       <c r="E35" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>127</v>
+      <c r="F35" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>32</v>
@@ -3614,8 +3602,8 @@
       <c r="E36" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>127</v>
+      <c r="F36" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>32</v>
@@ -3640,8 +3628,8 @@
       <c r="E37" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>127</v>
+      <c r="F37" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>32</v>
@@ -3666,8 +3654,8 @@
       <c r="E38" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>127</v>
+      <c r="F38" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>28</v>
@@ -3692,8 +3680,8 @@
       <c r="E39" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>127</v>
+      <c r="F39" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>32</v>
@@ -3718,8 +3706,8 @@
       <c r="E40" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>127</v>
+      <c r="F40" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>32</v>
@@ -3744,8 +3732,8 @@
       <c r="E41" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>127</v>
+      <c r="F41" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>32</v>
@@ -3770,8 +3758,8 @@
       <c r="E42" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>127</v>
+      <c r="F42" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>28</v>
@@ -3796,8 +3784,8 @@
       <c r="E43" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>127</v>
+      <c r="F43" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>32</v>
@@ -3822,8 +3810,8 @@
       <c r="E44" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>127</v>
+      <c r="F44" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>32</v>
@@ -3848,8 +3836,8 @@
       <c r="E45" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>127</v>
+      <c r="F45" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>32</v>
@@ -3877,8 +3865,8 @@
       <c r="E46" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>127</v>
+      <c r="F46" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>32</v>
@@ -3903,8 +3891,8 @@
       <c r="E47" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>127</v>
+      <c r="F47" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>32</v>
@@ -3929,8 +3917,8 @@
       <c r="E48" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>127</v>
+      <c r="F48" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>32</v>
@@ -3955,8 +3943,8 @@
       <c r="E49" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>127</v>
+      <c r="F49" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>55</v>
@@ -3981,8 +3969,8 @@
       <c r="E50" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>127</v>
+      <c r="F50" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>59</v>
@@ -4007,8 +3995,8 @@
       <c r="E51" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>127</v>
+      <c r="F51" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>59</v>
@@ -4033,8 +4021,8 @@
       <c r="E52" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>127</v>
+      <c r="F52" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>32</v>
@@ -4059,8 +4047,8 @@
       <c r="E53" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>127</v>
+      <c r="F53" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>32</v>
@@ -4085,8 +4073,8 @@
       <c r="E54" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>127</v>
+      <c r="F54" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>32</v>
@@ -4111,8 +4099,8 @@
       <c r="E55" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>127</v>
+      <c r="F55" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>32</v>
@@ -4137,8 +4125,8 @@
       <c r="E56" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>127</v>
+      <c r="F56" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>32</v>
@@ -4163,8 +4151,8 @@
       <c r="E57" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>127</v>
+      <c r="F57" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>32</v>
@@ -4189,8 +4177,8 @@
       <c r="E58" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>127</v>
+      <c r="F58" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>32</v>
@@ -4215,8 +4203,8 @@
       <c r="E59" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>127</v>
+      <c r="F59" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>32</v>
@@ -4241,8 +4229,8 @@
       <c r="E60" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>127</v>
+      <c r="F60" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>32</v>
@@ -4267,8 +4255,8 @@
       <c r="E61" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>127</v>
+      <c r="F61" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>59</v>
@@ -4293,8 +4281,8 @@
       <c r="E62" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>127</v>
+      <c r="F62" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>32</v>
@@ -4319,8 +4307,8 @@
       <c r="E63" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>127</v>
+      <c r="F63" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>32</v>
@@ -4345,8 +4333,8 @@
       <c r="E64" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>127</v>
+      <c r="F64" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>32</v>
@@ -4371,8 +4359,8 @@
       <c r="E65" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>127</v>
+      <c r="F65" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>32</v>
@@ -4397,8 +4385,8 @@
       <c r="E66" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="F66" s="4" t="s">
-        <v>127</v>
+      <c r="F66" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>32</v>
@@ -4423,8 +4411,8 @@
       <c r="E67" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>127</v>
+      <c r="F67" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>32</v>
@@ -4449,8 +4437,8 @@
       <c r="E68" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>127</v>
+      <c r="F68" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>32</v>
@@ -4475,8 +4463,8 @@
       <c r="E69" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F69" s="4" t="s">
-        <v>127</v>
+      <c r="F69" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>32</v>
@@ -4501,8 +4489,8 @@
       <c r="E70" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>127</v>
+      <c r="F70" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>32</v>
@@ -4527,8 +4515,8 @@
       <c r="E71" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F71" s="4" t="s">
-        <v>127</v>
+      <c r="F71" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>32</v>
@@ -4553,8 +4541,8 @@
       <c r="E72" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F72" s="4" t="s">
-        <v>127</v>
+      <c r="F72" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>32</v>
@@ -4579,8 +4567,8 @@
       <c r="E73" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F73" s="4" t="s">
-        <v>127</v>
+      <c r="F73" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>32</v>
@@ -4605,8 +4593,8 @@
       <c r="E74" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F74" s="4" t="s">
-        <v>127</v>
+      <c r="F74" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>32</v>
@@ -4631,8 +4619,8 @@
       <c r="E75" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F75" s="4" t="s">
-        <v>127</v>
+      <c r="F75" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>32</v>
@@ -4657,8 +4645,8 @@
       <c r="E76" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>127</v>
+      <c r="F76" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>32</v>
@@ -4683,8 +4671,8 @@
       <c r="E77" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F77" s="4" t="s">
-        <v>127</v>
+      <c r="F77" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>32</v>
@@ -4709,8 +4697,8 @@
       <c r="E78" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F78" s="4" t="s">
-        <v>127</v>
+      <c r="F78" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>32</v>
@@ -4735,8 +4723,8 @@
       <c r="E79" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="F79" s="4" t="s">
-        <v>127</v>
+      <c r="F79" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>32</v>
@@ -4761,8 +4749,8 @@
       <c r="E80" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F80" s="4" t="s">
-        <v>127</v>
+      <c r="F80" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>32</v>
@@ -4787,8 +4775,8 @@
       <c r="E81" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F81" s="4" t="s">
-        <v>127</v>
+      <c r="F81" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>32</v>
@@ -4813,8 +4801,8 @@
       <c r="E82" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F82" s="4" t="s">
-        <v>127</v>
+      <c r="F82" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>32</v>
@@ -4839,8 +4827,8 @@
       <c r="E83" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F83" s="4" t="s">
-        <v>127</v>
+      <c r="F83" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>32</v>
@@ -4865,8 +4853,8 @@
       <c r="E84" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>127</v>
+      <c r="F84" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>32</v>
@@ -4891,8 +4879,8 @@
       <c r="E85" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>127</v>
+      <c r="F85" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>32</v>
@@ -4917,8 +4905,8 @@
       <c r="E86" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F86" s="4" t="s">
-        <v>127</v>
+      <c r="F86" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>32</v>
@@ -4943,8 +4931,8 @@
       <c r="E87" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F87" s="4" t="s">
-        <v>127</v>
+      <c r="F87" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>32</v>
@@ -4969,8 +4957,8 @@
       <c r="E88" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>127</v>
+      <c r="F88" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G88" s="4" t="s">
         <v>32</v>
@@ -4995,8 +4983,8 @@
       <c r="E89" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F89" s="4" t="s">
-        <v>127</v>
+      <c r="F89" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>32</v>
@@ -5021,8 +5009,8 @@
       <c r="E90" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="F90" s="4" t="s">
-        <v>127</v>
+      <c r="F90" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>32</v>
@@ -5047,8 +5035,8 @@
       <c r="E91" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F91" s="4" t="s">
-        <v>127</v>
+      <c r="F91" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G91" s="4" t="s">
         <v>32</v>
@@ -5073,8 +5061,8 @@
       <c r="E92" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>127</v>
+      <c r="F92" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>32</v>
@@ -5099,8 +5087,8 @@
       <c r="E93" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F93" s="4" t="s">
-        <v>127</v>
+      <c r="F93" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G93" s="4" t="s">
         <v>32</v>
@@ -5125,8 +5113,8 @@
       <c r="E94" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="F94" s="4" t="s">
-        <v>127</v>
+      <c r="F94" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>32</v>
@@ -5151,8 +5139,8 @@
       <c r="E95" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F95" s="4" t="s">
-        <v>127</v>
+      <c r="F95" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>32</v>
@@ -5240,7 +5228,7 @@
       </c>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="5" t="s">
         <v>279</v>
       </c>
       <c r="B99" s="4" t="s">
@@ -5249,11 +5237,11 @@
       <c r="C99" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E99" s="4" t="s">
+      <c r="D99" s="5" t="s">
         <v>280</v>
+      </c>
+      <c r="E99" s="7">
+        <v>17</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>271</v>
@@ -5275,11 +5263,11 @@
       <c r="C100" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D100" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E100" s="4" t="s">
+      <c r="D100" s="5" t="s">
         <v>283</v>
+      </c>
+      <c r="E100" s="7">
+        <v>8</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>271</v>
@@ -5379,11 +5367,11 @@
       <c r="C104" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E104" s="4" t="s">
+      <c r="D104" s="7" t="s">
         <v>293</v>
+      </c>
+      <c r="E104" s="7">
+        <v>34</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>271</v>
@@ -5405,11 +5393,11 @@
       <c r="C105" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E105" s="4" t="s">
+      <c r="D105" s="5" t="s">
         <v>296</v>
+      </c>
+      <c r="E105" s="7">
+        <v>139</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>271</v>
@@ -5720,8 +5708,8 @@
       <c r="D117" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="E117" s="4" t="s">
-        <v>331</v>
+      <c r="E117" s="7">
+        <v>1.2</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>271</v>
@@ -5730,12 +5718,12 @@
         <v>32</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>24</v>
@@ -5744,10 +5732,10 @@
         <v>25</v>
       </c>
       <c r="D118" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="E118" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>335</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>271</v>
@@ -5761,7 +5749,7 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>24</v>
@@ -5782,12 +5770,12 @@
         <v>32</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>24</v>
@@ -5808,64 +5796,64 @@
         <v>32</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>118</v>
       </c>
       <c r="E121" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F121" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="F121" s="4" t="s">
+      <c r="G121" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H121" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>118</v>
       </c>
       <c r="E122" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H122" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>112</v>
@@ -5877,21 +5865,21 @@
         <v>122</v>
       </c>
       <c r="E123" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="F123" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="F123" s="4" t="s">
+      <c r="G123" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H123" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="G123" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>112</v>
@@ -5900,24 +5888,24 @@
         <v>113</v>
       </c>
       <c r="D124" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E124" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="E124" s="4" t="s">
+      <c r="F124" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="F124" s="4" t="s">
+      <c r="G124" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H124" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="G124" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H124" s="4" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>112</v>
@@ -5926,13 +5914,13 @@
         <v>19</v>
       </c>
       <c r="D125" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E125" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="E125" s="4" t="s">
-        <v>359</v>
-      </c>
       <c r="F125" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>32</v>
@@ -5943,7 +5931,7 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>112</v>
@@ -5952,24 +5940,24 @@
         <v>36</v>
       </c>
       <c r="D126" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E126" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="E126" s="4" t="s">
+      <c r="F126" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H126" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="G126" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>112</v>
@@ -5978,24 +5966,24 @@
         <v>19</v>
       </c>
       <c r="D127" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="E127" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="E127" s="4" t="s">
+      <c r="F127" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H127" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>112</v>
@@ -6004,50 +5992,50 @@
         <v>19</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E128" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H128" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C129" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="D129" s="4" t="s">
+      <c r="E129" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E129" s="4" t="s">
+      <c r="F129" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="F129" s="4" t="s">
+      <c r="G129" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H129" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>112</v>
@@ -6056,24 +6044,24 @@
         <v>36</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G130" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>112</v>
@@ -6082,39 +6070,39 @@
         <v>19</v>
       </c>
       <c r="D131" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="E131" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="E131" s="4" t="s">
+      <c r="F131" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H131" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="G131" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H131" s="4" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="B132" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E132" s="4" t="s">
+      <c r="F132" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>386</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>32</v>
@@ -6125,169 +6113,169 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C133" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D133" s="4" t="s">
+      <c r="E133" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="F133" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="E133" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="F133" s="4" t="s">
+      <c r="G133" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H133" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="G133" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H133" s="4" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>112</v>
       </c>
       <c r="E134" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H134" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C135" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="E135" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="F135" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="E135" s="4" t="s">
+      <c r="G135" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H135" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G135" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H135" s="4" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D136" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H136" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="E136" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="F136" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G136" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H136" s="4" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>96</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B138" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="C138" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E138" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="C138" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="E138" s="4" t="s">
+      <c r="F138" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H138" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G138" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H138" s="4" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>18</v>
@@ -6296,128 +6284,128 @@
         <v>103</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B140" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="C140" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="E140" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="C140" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D140" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="E140" s="4" t="s">
+      <c r="F140" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H140" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E141" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H141" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G141" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H141" s="4" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>112</v>
       </c>
       <c r="E142" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H142" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G142" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B143" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="B143" s="4" t="s">
-        <v>421</v>
-      </c>
       <c r="C143" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>132</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>276</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>276</v>
@@ -6426,102 +6414,102 @@
         <v>95</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G144" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E145" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H145" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G145" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H145" s="4" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B146" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="C146" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H146" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G146" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H146" s="4" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B147" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="B147" s="4" t="s">
-        <v>432</v>
-      </c>
       <c r="C147" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E147" s="7">
         <v>25</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>102</v>
@@ -6530,128 +6518,128 @@
         <v>21</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>130</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>179</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C151" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D151" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="E151" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="F151" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="E151" s="4" t="s">
+      <c r="G151" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H151" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="F151" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G151" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H151" s="4" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D152" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="B152" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D152" s="5" t="s">
+      <c r="E152" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="E152" s="4" t="s">
+      <c r="F152" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G152" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H152" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="F152" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G152" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H152" s="4" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>24</v>
@@ -6660,206 +6648,206 @@
         <v>65</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G153" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B154" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="C154" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="E154" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="C154" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D154" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="E154" s="4" t="s">
+      <c r="F154" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H154" s="4" t="s">
         <v>451</v>
-      </c>
-      <c r="F154" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G154" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H154" s="4" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>171</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E156" s="7">
         <v>282</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E157" s="7">
         <v>228</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E158" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H158" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="F158" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G158" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H158" s="4" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D159" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="E159" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="E159" s="4" t="s">
+      <c r="F159" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H159" s="4" t="s">
         <v>465</v>
-      </c>
-      <c r="F159" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G159" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H159" s="4" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E160" s="7">
         <v>0.9</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>102</v>
@@ -6868,180 +6856,180 @@
         <v>11.3</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C162" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D162" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D162" s="4" t="s">
+      <c r="E162" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="F162" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="E162" s="4" t="s">
+      <c r="G162" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H162" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="F162" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G162" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H162" s="4" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E163" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="B163" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="E163" s="4" t="s">
+      <c r="F163" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H163" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="F163" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G163" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H163" s="4" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D164" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="B164" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D164" s="4" t="s">
+      <c r="E164" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="E164" s="4" t="s">
+      <c r="F164" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H164" s="4" t="s">
         <v>479</v>
-      </c>
-      <c r="F164" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G164" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H164" s="4" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C165" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D165" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D165" s="4" t="s">
+      <c r="E165" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="F165" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="E165" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="F165" s="4" t="s">
-        <v>390</v>
-      </c>
       <c r="G165" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D166" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="E166" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="E166" s="4" t="s">
+      <c r="F166" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G166" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H166" s="4" t="s">
         <v>485</v>
-      </c>
-      <c r="F166" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G166" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H166" s="4" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E167" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="B167" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="D167" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="E167" s="4" t="s">
+      <c r="F167" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H167" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="F167" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G167" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H167" s="4" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>112</v>
@@ -7050,70 +7038,70 @@
         <v>155</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E169" s="7">
         <v>370</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>150</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>35</v>
@@ -7122,13 +7110,13 @@
         <v>11</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E171" s="4">
         <v>4</v>
       </c>
-      <c r="F171" s="4" t="s">
-        <v>127</v>
+      <c r="F171" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>32</v>
@@ -7139,7 +7127,7 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>102</v>
@@ -7153,8 +7141,8 @@
       <c r="E172" s="4">
         <v>28</v>
       </c>
-      <c r="F172" s="4" t="s">
-        <v>127</v>
+      <c r="F172" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>32</v>
@@ -7165,7 +7153,7 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>35</v>
@@ -7179,8 +7167,8 @@
       <c r="E173" s="4">
         <v>29</v>
       </c>
-      <c r="F173" s="4" t="s">
-        <v>127</v>
+      <c r="F173" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>32</v>
@@ -7191,16 +7179,16 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>276</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E174" s="4">
         <v>150</v>
@@ -7217,7 +7205,7 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>10</v>
@@ -7243,7 +7231,7 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>10</v>
@@ -7257,8 +7245,8 @@
       <c r="E176" s="4">
         <v>13.8</v>
       </c>
-      <c r="F176" s="4" t="s">
-        <v>127</v>
+      <c r="F176" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>32</v>
@@ -7269,7 +7257,7 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>10</v>
@@ -7283,8 +7271,8 @@
       <c r="E177" s="4">
         <v>6.5</v>
       </c>
-      <c r="F177" s="4" t="s">
-        <v>127</v>
+      <c r="F177" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G177" s="4" t="s">
         <v>32</v>
@@ -7295,7 +7283,7 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>10</v>
@@ -7309,8 +7297,8 @@
       <c r="E178" s="4">
         <v>7.63</v>
       </c>
-      <c r="F178" s="4" t="s">
-        <v>127</v>
+      <c r="F178" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>32</v>
@@ -7321,7 +7309,7 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>10</v>
@@ -7335,8 +7323,8 @@
       <c r="E179" s="4">
         <v>21</v>
       </c>
-      <c r="F179" s="4" t="s">
-        <v>127</v>
+      <c r="F179" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>32</v>
@@ -7347,7 +7335,7 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>10</v>
@@ -7361,8 +7349,8 @@
       <c r="E180" s="4">
         <v>7.5</v>
       </c>
-      <c r="F180" s="4" t="s">
-        <v>127</v>
+      <c r="F180" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>32</v>
@@ -7373,7 +7361,7 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>10</v>
@@ -7387,8 +7375,8 @@
       <c r="E181" s="4">
         <v>4.5</v>
       </c>
-      <c r="F181" s="4" t="s">
-        <v>127</v>
+      <c r="F181" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>32</v>
@@ -7399,7 +7387,7 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>10</v>
@@ -7413,8 +7401,8 @@
       <c r="E182" s="4">
         <v>12.5</v>
       </c>
-      <c r="F182" s="4" t="s">
-        <v>127</v>
+      <c r="F182" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>32</v>
@@ -7425,7 +7413,7 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>10</v>
@@ -7439,8 +7427,8 @@
       <c r="E183" s="4">
         <v>5</v>
       </c>
-      <c r="F183" s="4" t="s">
-        <v>127</v>
+      <c r="F183" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>32</v>
@@ -7451,22 +7439,22 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E184" s="4">
         <v>0.7</v>
       </c>
-      <c r="F184" s="4" t="s">
-        <v>127</v>
+      <c r="F184" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>32</v>
@@ -7477,7 +7465,7 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>10</v>
@@ -7491,8 +7479,8 @@
       <c r="E185" s="4">
         <v>30.52</v>
       </c>
-      <c r="F185" s="4" t="s">
-        <v>127</v>
+      <c r="F185" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>32</v>
@@ -7503,7 +7491,7 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>10</v>
@@ -7517,8 +7505,8 @@
       <c r="E186" s="4">
         <v>10</v>
       </c>
-      <c r="F186" s="4" t="s">
-        <v>127</v>
+      <c r="F186" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>32</v>
@@ -7529,7 +7517,7 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>10</v>
@@ -7543,8 +7531,8 @@
       <c r="E187" s="4">
         <v>20</v>
       </c>
-      <c r="F187" s="4" t="s">
-        <v>127</v>
+      <c r="F187" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>32</v>
@@ -7555,7 +7543,7 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>10</v>
@@ -7569,8 +7557,8 @@
       <c r="E188" s="4">
         <v>8.5</v>
       </c>
-      <c r="F188" s="4" t="s">
-        <v>127</v>
+      <c r="F188" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>32</v>
@@ -7581,7 +7569,7 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>10</v>
@@ -7595,8 +7583,8 @@
       <c r="E189" s="4">
         <v>8.5</v>
       </c>
-      <c r="F189" s="4" t="s">
-        <v>127</v>
+      <c r="F189" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>32</v>
@@ -7607,7 +7595,7 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>35</v>
@@ -7621,8 +7609,8 @@
       <c r="E190" s="4">
         <v>5.5</v>
       </c>
-      <c r="F190" s="4" t="s">
-        <v>127</v>
+      <c r="F190" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G190" s="4" t="s">
         <v>32</v>
@@ -7633,7 +7621,7 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>10</v>
@@ -7647,8 +7635,8 @@
       <c r="E191" s="4">
         <v>20</v>
       </c>
-      <c r="F191" s="4" t="s">
-        <v>127</v>
+      <c r="F191" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G191" s="4" t="s">
         <v>32</v>
@@ -7659,7 +7647,7 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>10</v>
@@ -7673,8 +7661,8 @@
       <c r="E192" s="4">
         <v>5</v>
       </c>
-      <c r="F192" s="4" t="s">
-        <v>127</v>
+      <c r="F192" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G192" s="4" t="s">
         <v>32</v>
@@ -7685,7 +7673,7 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B193" s="4" t="s">
         <v>10</v>
@@ -7699,8 +7687,8 @@
       <c r="E193" s="4">
         <v>10</v>
       </c>
-      <c r="F193" s="4" t="s">
-        <v>127</v>
+      <c r="F193" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G193" s="4" t="s">
         <v>32</v>
@@ -7711,13 +7699,13 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>12</v>
@@ -7725,8 +7713,8 @@
       <c r="E194" s="4">
         <v>28</v>
       </c>
-      <c r="F194" s="4" t="s">
-        <v>127</v>
+      <c r="F194" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G194" s="4" t="s">
         <v>32</v>
@@ -7737,7 +7725,7 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="4" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>35</v>
@@ -7751,8 +7739,8 @@
       <c r="E195" s="4">
         <v>18</v>
       </c>
-      <c r="F195" s="4" t="s">
-        <v>127</v>
+      <c r="F195" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G195" s="4" t="s">
         <v>32</v>
@@ -7763,7 +7751,7 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>24</v>
@@ -7777,8 +7765,8 @@
       <c r="E196" s="4">
         <v>18</v>
       </c>
-      <c r="F196" s="4" t="s">
-        <v>127</v>
+      <c r="F196" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G196" s="4" t="s">
         <v>32</v>
@@ -7789,7 +7777,7 @@
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="4" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>10</v>
@@ -7803,8 +7791,8 @@
       <c r="E197" s="4">
         <v>4</v>
       </c>
-      <c r="F197" s="4" t="s">
-        <v>127</v>
+      <c r="F197" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G197" s="4" t="s">
         <v>32</v>
@@ -7815,7 +7803,7 @@
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="4" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>10</v>
@@ -7829,8 +7817,8 @@
       <c r="E198" s="4">
         <v>2.6</v>
       </c>
-      <c r="F198" s="4" t="s">
-        <v>127</v>
+      <c r="F198" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G198" s="4" t="s">
         <v>32</v>
@@ -7841,7 +7829,7 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="4" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>10</v>
@@ -7855,8 +7843,8 @@
       <c r="E199" s="4">
         <v>26.5</v>
       </c>
-      <c r="F199" s="4" t="s">
-        <v>127</v>
+      <c r="F199" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G199" s="4" t="s">
         <v>32</v>
@@ -7867,7 +7855,7 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="4" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>10</v>
@@ -7881,8 +7869,8 @@
       <c r="E200" s="4">
         <v>3</v>
       </c>
-      <c r="F200" s="4" t="s">
-        <v>127</v>
+      <c r="F200" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>32</v>
@@ -7893,7 +7881,7 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="4" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>10</v>
@@ -7907,8 +7895,8 @@
       <c r="E201" s="4">
         <v>6</v>
       </c>
-      <c r="F201" s="4" t="s">
-        <v>127</v>
+      <c r="F201" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>32</v>
@@ -7919,7 +7907,7 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="4" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>10</v>
@@ -7933,8 +7921,8 @@
       <c r="E202" s="4">
         <v>1.5</v>
       </c>
-      <c r="F202" s="4" t="s">
-        <v>127</v>
+      <c r="F202" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G202" s="4" t="s">
         <v>32</v>
@@ -7945,7 +7933,7 @@
     </row>
     <row r="203" spans="1:8">
       <c r="A203" s="4" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>10</v>
@@ -7959,8 +7947,8 @@
       <c r="E203" s="4">
         <v>17</v>
       </c>
-      <c r="F203" s="4" t="s">
-        <v>127</v>
+      <c r="F203" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G203" s="4" t="s">
         <v>32</v>
@@ -7971,13 +7959,13 @@
     </row>
     <row r="204" spans="1:8">
       <c r="A204" s="4" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>12</v>
@@ -7985,8 +7973,8 @@
       <c r="E204" s="4">
         <v>38</v>
       </c>
-      <c r="F204" s="4" t="s">
-        <v>127</v>
+      <c r="F204" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G204" s="4" t="s">
         <v>32</v>
@@ -7997,7 +7985,7 @@
     </row>
     <row r="205" spans="1:8">
       <c r="A205" s="4" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B205" s="4" t="s">
         <v>10</v>
@@ -8011,8 +7999,8 @@
       <c r="E205" s="4">
         <v>5.5</v>
       </c>
-      <c r="F205" s="4" t="s">
-        <v>127</v>
+      <c r="F205" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G205" s="4" t="s">
         <v>32</v>
@@ -8023,7 +8011,7 @@
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="4" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>10</v>
@@ -8037,8 +8025,8 @@
       <c r="E206" s="4">
         <v>7.8</v>
       </c>
-      <c r="F206" s="4" t="s">
-        <v>127</v>
+      <c r="F206" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>32</v>
@@ -8049,7 +8037,7 @@
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="4" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>10</v>
@@ -8063,8 +8051,8 @@
       <c r="E207" s="4">
         <v>6.5</v>
       </c>
-      <c r="F207" s="4" t="s">
-        <v>127</v>
+      <c r="F207" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>32</v>
@@ -8075,7 +8063,7 @@
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="4" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>10</v>
@@ -8089,8 +8077,8 @@
       <c r="E208" s="4">
         <v>6.5</v>
       </c>
-      <c r="F208" s="4" t="s">
-        <v>127</v>
+      <c r="F208" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>32</v>
@@ -8101,7 +8089,7 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="4" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B209" s="4" t="s">
         <v>35</v>
@@ -8109,14 +8097,14 @@
       <c r="C209" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D209" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E209" s="4">
-        <v>40</v>
-      </c>
-      <c r="F209" s="4" t="s">
-        <v>127</v>
+      <c r="D209" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="E209" s="7">
+        <v>34</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>32</v>
@@ -8127,13 +8115,13 @@
     </row>
     <row r="210" spans="1:8">
       <c r="A210" s="4" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D210" s="4" t="s">
         <v>12</v>
@@ -8141,8 +8129,8 @@
       <c r="E210" s="4">
         <v>30</v>
       </c>
-      <c r="F210" s="4" t="s">
-        <v>127</v>
+      <c r="F210" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>32</v>
@@ -8153,7 +8141,7 @@
     </row>
     <row r="211" spans="1:8">
       <c r="A211" s="4" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>10</v>
@@ -8167,8 +8155,8 @@
       <c r="E211" s="4">
         <v>3</v>
       </c>
-      <c r="F211" s="4" t="s">
-        <v>127</v>
+      <c r="F211" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>32</v>
@@ -8179,7 +8167,7 @@
     </row>
     <row r="212" spans="1:8">
       <c r="A212" s="4" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>35</v>
@@ -8193,8 +8181,8 @@
       <c r="E212" s="4">
         <v>7</v>
       </c>
-      <c r="F212" s="4" t="s">
-        <v>127</v>
+      <c r="F212" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>32</v>
@@ -8205,7 +8193,7 @@
     </row>
     <row r="213" spans="1:8">
       <c r="A213" s="4" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B213" s="4" t="s">
         <v>10</v>
@@ -8231,7 +8219,7 @@
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="4" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B214" s="4" t="s">
         <v>10</v>
@@ -8245,8 +8233,8 @@
       <c r="E214" s="4">
         <v>5</v>
       </c>
-      <c r="F214" s="4" t="s">
-        <v>127</v>
+      <c r="F214" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G214" s="4" t="s">
         <v>32</v>
@@ -8257,7 +8245,7 @@
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="4" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>112</v>
@@ -8266,13 +8254,13 @@
         <v>11</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E215" s="4">
         <v>235</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>32</v>
@@ -8283,7 +8271,7 @@
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="4" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B216" s="4" t="s">
         <v>24</v>
@@ -8292,13 +8280,13 @@
         <v>11</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E216" s="4">
         <v>23</v>
       </c>
-      <c r="F216" s="4" t="s">
-        <v>127</v>
+      <c r="F216" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>32</v>
@@ -8309,7 +8297,7 @@
     </row>
     <row r="217" spans="1:8">
       <c r="A217" s="4" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>18</v>
@@ -8318,13 +8306,13 @@
         <v>11</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E217" s="4">
         <v>47.5</v>
       </c>
-      <c r="F217" s="4" t="s">
-        <v>127</v>
+      <c r="F217" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G217" s="4" t="s">
         <v>32</v>
@@ -8335,7 +8323,7 @@
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="4" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>112</v>
@@ -8361,22 +8349,22 @@
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="4" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E219" s="4">
         <v>0.24</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>32</v>
@@ -8387,22 +8375,22 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="4" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B220" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E220" s="4">
         <v>0.95</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>32</v>
@@ -8413,22 +8401,22 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="4" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E221" s="4">
         <v>15</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>32</v>
@@ -8439,22 +8427,22 @@
     </row>
     <row r="222" spans="1:8">
       <c r="A222" s="4" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E222" s="4">
         <v>2.8</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>32</v>
@@ -8465,22 +8453,22 @@
     </row>
     <row r="223" spans="1:8">
       <c r="A223" s="4" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>276</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E223" s="4">
         <v>45</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>32</v>
@@ -8491,22 +8479,22 @@
     </row>
     <row r="224" spans="1:8">
       <c r="A224" s="4" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E224" s="7">
         <v>28</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G224" s="4" t="s">
         <v>32</v>
@@ -8517,22 +8505,22 @@
     </row>
     <row r="225" spans="1:8">
       <c r="A225" s="4" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E225" s="4">
         <v>18</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G225" s="4" t="s">
         <v>32</v>
@@ -8543,22 +8531,22 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="4" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E226" s="4">
         <v>10</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G226" s="4" t="s">
         <v>32</v>
@@ -8569,22 +8557,22 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="5" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B227" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E227" s="4">
         <v>580</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>32</v>
@@ -8595,22 +8583,22 @@
     </row>
     <row r="228" spans="1:8">
       <c r="A228" s="4" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C228" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D228" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="D228" s="4" t="s">
-        <v>389</v>
       </c>
       <c r="E228" s="4">
         <v>180</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G228" s="4" t="s">
         <v>32</v>
@@ -8621,22 +8609,22 @@
     </row>
     <row r="229" spans="1:8">
       <c r="A229" s="4" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E229" s="4">
         <v>65</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>32</v>
@@ -8647,22 +8635,22 @@
     </row>
     <row r="230" spans="1:8">
       <c r="A230" s="4" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>726</v>
+        <v>569</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E230" s="7">
         <v>10</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>32</v>
@@ -8673,22 +8661,22 @@
     </row>
     <row r="231" spans="1:8">
       <c r="A231" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B231" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E231" s="4">
         <v>114</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>32</v>
@@ -8699,22 +8687,22 @@
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B232" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E232" s="7">
         <v>66</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>32</v>
@@ -8725,22 +8713,22 @@
     </row>
     <row r="233" spans="1:8">
       <c r="A233" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B233" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E233" s="7">
         <v>114</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>32</v>
@@ -8751,22 +8739,22 @@
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B234" s="4" t="s">
         <v>276</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E234" s="4">
         <v>95</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>32</v>
@@ -8777,22 +8765,22 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E235" s="4">
         <v>170</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>32</v>
@@ -8803,22 +8791,22 @@
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B236" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E236" s="4">
         <v>27</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G236" s="4" t="s">
         <v>32</v>
@@ -8829,7 +8817,7 @@
     </row>
     <row r="237" spans="1:8">
       <c r="A237" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B237" s="4" t="s">
         <v>45</v>
@@ -8838,7 +8826,7 @@
         <v>106</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E237" s="4">
         <v>15</v>
@@ -8855,7 +8843,7 @@
     </row>
     <row r="238" spans="1:8">
       <c r="A238" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B238" s="4" t="s">
         <v>276</v>
@@ -8864,7 +8852,7 @@
         <v>106</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E238" s="4">
         <v>28</v>
@@ -8881,7 +8869,7 @@
     </row>
     <row r="239" spans="1:8">
       <c r="A239" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B239" s="4" t="s">
         <v>35</v>
@@ -8907,7 +8895,7 @@
     </row>
     <row r="240" spans="1:8">
       <c r="A240" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B240" s="4" t="s">
         <v>276</v>
@@ -8959,7 +8947,7 @@
     </row>
     <row r="242" spans="1:8">
       <c r="A242" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B242" s="4" t="s">
         <v>24</v>
@@ -8968,7 +8956,7 @@
         <v>25</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E242" s="4">
         <v>13</v>
@@ -8985,7 +8973,7 @@
     </row>
     <row r="243" spans="1:8">
       <c r="A243" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B243" s="4" t="s">
         <v>24</v>
@@ -8994,7 +8982,7 @@
         <v>25</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E243" s="4">
         <v>13.5</v>
@@ -9011,7 +8999,7 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B244" s="4" t="s">
         <v>24</v>
@@ -9020,7 +9008,7 @@
         <v>25</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E244" s="4">
         <v>92</v>
@@ -9037,7 +9025,7 @@
     </row>
     <row r="245" spans="1:8">
       <c r="A245" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B245" s="4" t="s">
         <v>10</v>
@@ -9063,7 +9051,7 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B246" s="4" t="s">
         <v>24</v>
@@ -9072,7 +9060,7 @@
         <v>25</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E246" s="4">
         <v>9</v>
@@ -9089,7 +9077,7 @@
     </row>
     <row r="247" spans="1:8">
       <c r="A247" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>35</v>
@@ -9098,7 +9086,7 @@
         <v>25</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E247" s="4">
         <v>26</v>
@@ -9115,7 +9103,7 @@
     </row>
     <row r="248" spans="1:8">
       <c r="A248" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B248" s="4" t="s">
         <v>24</v>
@@ -9141,7 +9129,7 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>18</v>
@@ -9167,22 +9155,22 @@
     </row>
     <row r="250" spans="1:8">
       <c r="A250" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B250" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>600</v>
+        <v>283</v>
       </c>
       <c r="E250" s="4">
         <v>180</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>109</v>
@@ -9193,22 +9181,22 @@
     </row>
     <row r="251" spans="1:8">
       <c r="A251" s="4" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B251" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E251" s="4">
         <v>68</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>109</v>
@@ -9219,22 +9207,22 @@
     </row>
     <row r="252" spans="1:8">
       <c r="A252" s="4" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B252" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E252" s="4">
         <v>80</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>109</v>
@@ -9245,7 +9233,7 @@
     </row>
     <row r="253" spans="1:8">
       <c r="A253" s="4" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B253" s="4" t="s">
         <v>35</v>
@@ -9254,7 +9242,7 @@
         <v>106</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>600</v>
+        <v>283</v>
       </c>
       <c r="E253" s="4">
         <v>3.5</v>
@@ -9271,7 +9259,7 @@
     </row>
     <row r="254" spans="1:8">
       <c r="A254" s="4" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B254" s="4" t="s">
         <v>45</v>
@@ -9280,7 +9268,7 @@
         <v>106</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E254" s="4">
         <v>12</v>
@@ -9297,7 +9285,7 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255" s="4" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B255" s="4" t="s">
         <v>112</v>
@@ -9306,7 +9294,7 @@
         <v>106</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E255" s="4">
         <v>297.5</v>
@@ -9323,7 +9311,7 @@
     </row>
     <row r="256" spans="1:8">
       <c r="A256" s="4" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B256" s="4" t="s">
         <v>35</v>
@@ -9332,13 +9320,13 @@
         <v>19</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E256" s="4">
         <v>4.5</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G256" s="4" t="s">
         <v>109</v>
@@ -9349,7 +9337,7 @@
     </row>
     <row r="257" spans="1:8">
       <c r="A257" s="4" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B257" s="4" t="s">
         <v>24</v>
@@ -9358,7 +9346,7 @@
         <v>25</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>600</v>
+        <v>283</v>
       </c>
       <c r="E257" s="4">
         <v>8</v>
@@ -9367,7 +9355,7 @@
         <v>271</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H257" s="4">
         <v>1006062</v>
@@ -9375,7 +9363,7 @@
     </row>
     <row r="258" spans="1:8">
       <c r="A258" s="4" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B258" s="4" t="s">
         <v>10</v>
@@ -9389,11 +9377,11 @@
       <c r="E258" s="4">
         <v>14.5</v>
       </c>
-      <c r="F258" s="4" t="s">
-        <v>616</v>
+      <c r="F258" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H258" s="4">
         <v>1006067</v>
@@ -9401,7 +9389,7 @@
     </row>
     <row r="259" spans="1:8">
       <c r="A259" s="4" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B259" s="4" t="s">
         <v>35</v>
@@ -9409,17 +9397,17 @@
       <c r="C259" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D259" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E259" s="4">
-        <v>32</v>
+      <c r="D259" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="E259" s="7">
+        <v>87.5</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>618</v>
+        <v>354</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H259" s="4">
         <v>1009027</v>
@@ -9427,7 +9415,7 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260" s="4" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B260" s="4" t="s">
         <v>276</v>
@@ -9436,7 +9424,7 @@
         <v>25</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E260" s="4">
         <v>226</v>
@@ -9445,7 +9433,7 @@
         <v>271</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H260" s="4">
         <v>1005009</v>
@@ -9453,7 +9441,7 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261" s="11" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B261" s="11" t="s">
         <v>10</v>
@@ -9467,8 +9455,8 @@
       <c r="E261" s="6">
         <v>48.5</v>
       </c>
-      <c r="F261" s="6" t="s">
-        <v>616</v>
+      <c r="F261" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G261" s="12" t="s">
         <v>32</v>
@@ -9479,7 +9467,7 @@
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B262" s="11" t="s">
         <v>10</v>
@@ -9505,7 +9493,7 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263" s="11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B263" s="11" t="s">
         <v>24</v>
@@ -9531,7 +9519,7 @@
     </row>
     <row r="264" spans="1:8">
       <c r="A264" s="11" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B264" s="11" t="s">
         <v>24</v>
@@ -9540,13 +9528,13 @@
         <v>106</v>
       </c>
       <c r="D264" s="11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E264" s="6">
         <v>30</v>
       </c>
       <c r="F264" s="6" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G264" s="13" t="s">
         <v>109</v>
@@ -9557,7 +9545,7 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B265" s="11" t="s">
         <v>24</v>
@@ -9583,7 +9571,7 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B266" s="11" t="s">
         <v>10</v>
@@ -9609,7 +9597,7 @@
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="11" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B267" s="11" t="s">
         <v>24</v>
@@ -9618,13 +9606,13 @@
         <v>25</v>
       </c>
       <c r="D267" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E267" s="6">
         <v>117.6</v>
       </c>
       <c r="F267" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G267" s="12" t="s">
         <v>32</v>
@@ -9635,7 +9623,7 @@
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="11" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B268" s="11" t="s">
         <v>24</v>
@@ -9644,13 +9632,13 @@
         <v>106</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E268" s="6">
         <v>38</v>
       </c>
       <c r="F268" s="6" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G268" s="13" t="s">
         <v>109</v>
@@ -9661,7 +9649,7 @@
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="11" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B269" s="11" t="s">
         <v>35</v>
@@ -9675,11 +9663,11 @@
       <c r="E269" s="6">
         <v>255</v>
       </c>
-      <c r="F269" s="6" t="s">
-        <v>634</v>
+      <c r="F269" s="4" t="s">
+        <v>374</v>
       </c>
       <c r="G269" s="12" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H269" s="11">
         <v>1006064</v>
@@ -9687,7 +9675,7 @@
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="5" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B270" s="5" t="s">
         <v>10</v>
@@ -9701,8 +9689,8 @@
       <c r="E270" s="7">
         <v>26</v>
       </c>
-      <c r="F270" s="5" t="s">
-        <v>616</v>
+      <c r="F270" s="25" t="s">
+        <v>613</v>
       </c>
       <c r="G270" s="5" t="s">
         <v>32</v>
@@ -9713,7 +9701,7 @@
     </row>
     <row r="271" spans="1:8">
       <c r="A271" s="15" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B271" s="15" t="s">
         <v>10</v>
@@ -9727,11 +9715,11 @@
       <c r="E271" s="16">
         <v>18</v>
       </c>
-      <c r="F271" s="15" t="s">
-        <v>616</v>
+      <c r="F271" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="G271" s="15" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H271" s="16">
         <v>1006070</v>
@@ -9739,7 +9727,7 @@
     </row>
     <row r="272" spans="1:8">
       <c r="A272" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B272" s="11" t="s">
         <v>10</v>
@@ -9754,7 +9742,7 @@
         <v>20</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G272" s="9" t="s">
         <v>55</v>
@@ -9765,7 +9753,7 @@
     </row>
     <row r="273" spans="1:8">
       <c r="A273" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B273" s="11" t="s">
         <v>10</v>
@@ -9780,7 +9768,7 @@
         <v>20</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G273" s="9" t="s">
         <v>55</v>
@@ -9791,7 +9779,7 @@
     </row>
     <row r="274" spans="1:8">
       <c r="A274" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B274" s="11" t="s">
         <v>24</v>
@@ -9800,7 +9788,7 @@
         <v>25</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E274" s="11">
         <v>50</v>
@@ -9817,10 +9805,10 @@
     </row>
     <row r="275" spans="1:8">
       <c r="A275" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B275" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>11</v>
@@ -9832,10 +9820,10 @@
         <v>90</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G275" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H275" s="6">
         <v>1001109</v>
@@ -9843,7 +9831,7 @@
     </row>
     <row r="276" spans="1:8">
       <c r="A276" s="11" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>10</v>
@@ -9858,7 +9846,7 @@
         <v>50</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>127</v>
+        <v>613</v>
       </c>
       <c r="G276" s="9" t="s">
         <v>15</v>
@@ -9869,16 +9857,16 @@
     </row>
     <row r="277" spans="1:8">
       <c r="A277" s="18" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B277" s="11" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C277" s="9" t="s">
         <v>19</v>
       </c>
       <c r="D277" s="11" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E277" s="11">
         <v>43.5</v>
@@ -9895,7 +9883,7 @@
     </row>
     <row r="278" spans="1:8">
       <c r="A278" s="11" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>35</v>
@@ -9921,7 +9909,7 @@
     </row>
     <row r="279" spans="1:8">
       <c r="A279" s="11" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B279" s="11" t="s">
         <v>10</v>
@@ -9936,18 +9924,18 @@
         <v>62</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G279" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H279" s="20" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="280" spans="1:8">
       <c r="A280" s="11" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>35</v>
@@ -9965,7 +9953,7 @@
         <v>14</v>
       </c>
       <c r="G280" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H280" s="17">
         <v>1009036</v>
@@ -9973,7 +9961,7 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281" s="21" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B281" s="11" t="s">
         <v>35</v>
@@ -9991,7 +9979,7 @@
         <v>14</v>
       </c>
       <c r="G281" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H281" s="17">
         <v>1009035</v>
@@ -9999,7 +9987,7 @@
     </row>
     <row r="282" spans="1:8">
       <c r="A282" s="11" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B282" s="11" t="s">
         <v>10</v>
@@ -10014,10 +10002,10 @@
         <v>5</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G282" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H282" s="17">
         <v>1001038</v>
@@ -10025,7 +10013,7 @@
     </row>
     <row r="283" spans="1:8">
       <c r="A283" s="11" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B283" s="11" t="s">
         <v>10</v>
@@ -10040,10 +10028,10 @@
         <v>3.5</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G283" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H283" s="17">
         <v>1001110</v>
@@ -10051,7 +10039,7 @@
     </row>
     <row r="284" spans="1:8">
       <c r="A284" s="11" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B284" s="11" t="s">
         <v>10</v>
@@ -10066,10 +10054,10 @@
         <v>3.5</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G284" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H284" s="17">
         <v>1001111</v>
@@ -10077,7 +10065,7 @@
     </row>
     <row r="285" spans="1:8">
       <c r="A285" s="11" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B285" s="11" t="s">
         <v>10</v>
@@ -10092,10 +10080,10 @@
         <v>180</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G285" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H285" s="17">
         <v>1007014</v>
@@ -10103,7 +10091,7 @@
     </row>
     <row r="286" spans="1:8">
       <c r="A286" s="11" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>10</v>
@@ -10118,18 +10106,18 @@
         <v>150</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G286" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H286" s="20" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="11" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B287" s="11" t="s">
         <v>10</v>
@@ -10144,18 +10132,18 @@
         <v>6.5</v>
       </c>
       <c r="F287" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G287" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H287" s="20" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" s="11" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B288" s="11" t="s">
         <v>10</v>
@@ -10170,18 +10158,18 @@
         <v>11.5</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G288" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H288" s="17">
-        <v>1003301</v>
+        <v>1003027</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" s="11" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B289" s="11" t="s">
         <v>10</v>
@@ -10196,10 +10184,10 @@
         <v>8</v>
       </c>
       <c r="F289" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G289" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H289" s="17">
         <v>1001113</v>
@@ -10208,7 +10196,7 @@
     </row>
     <row r="290" spans="1:8">
       <c r="A290" s="11" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>10</v>
@@ -10223,10 +10211,10 @@
         <v>6.5</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G290" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H290" s="17">
         <v>1001050</v>
@@ -10234,7 +10222,7 @@
     </row>
     <row r="291" spans="1:8">
       <c r="A291" s="11" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B291" s="11" t="s">
         <v>35</v>
@@ -10249,10 +10237,10 @@
         <v>6.5</v>
       </c>
       <c r="F291" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G291" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H291" s="17">
         <v>1001114</v>
@@ -10260,7 +10248,7 @@
     </row>
     <row r="292" spans="1:8">
       <c r="A292" s="11" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B292" s="11" t="s">
         <v>10</v>
@@ -10275,10 +10263,10 @@
         <v>5</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G292" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H292" s="17">
         <v>1001115</v>
@@ -10286,7 +10274,7 @@
     </row>
     <row r="293" spans="1:8">
       <c r="A293" s="11" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B293" s="11" t="s">
         <v>10</v>
@@ -10301,10 +10289,10 @@
         <v>18.5</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G293" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H293" s="17">
         <v>1003012</v>
@@ -10312,7 +10300,7 @@
     </row>
     <row r="294" spans="1:8">
       <c r="A294" s="11" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B294" s="11" t="s">
         <v>10</v>
@@ -10327,10 +10315,10 @@
         <v>7.5</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G294" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H294" s="17">
         <v>1002005</v>
@@ -10338,7 +10326,7 @@
     </row>
     <row r="295" spans="1:8">
       <c r="A295" s="11" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="B295" s="11" t="s">
         <v>10</v>
@@ -10353,10 +10341,10 @@
         <v>16</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G295" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H295" s="17">
         <v>1001116</v>
@@ -10364,7 +10352,7 @@
     </row>
     <row r="296" spans="1:8">
       <c r="A296" s="11" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>10</v>
@@ -10379,18 +10367,18 @@
         <v>8.6</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G296" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H296" s="20" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" s="11" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B297" s="11" t="s">
         <v>10</v>
@@ -10405,10 +10393,10 @@
         <v>20</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G297" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H297" s="17">
         <v>1001117</v>
@@ -10416,7 +10404,7 @@
     </row>
     <row r="298" spans="1:8">
       <c r="A298" s="11" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>10</v>
@@ -10431,10 +10419,10 @@
         <v>7.5</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G298" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H298" s="17">
         <v>1001118</v>
@@ -10442,7 +10430,7 @@
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="11" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B299" s="11" t="s">
         <v>35</v>
@@ -10457,10 +10445,10 @@
         <v>32.8</v>
       </c>
       <c r="F299" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G299" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H299" s="17">
         <v>1001119</v>
@@ -10468,7 +10456,7 @@
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="11" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>10</v>
@@ -10483,10 +10471,10 @@
         <v>4</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G300" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H300" s="17">
         <v>1001120</v>
@@ -10494,7 +10482,7 @@
     </row>
     <row r="301" spans="1:8">
       <c r="A301" s="11" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B301" s="11" t="s">
         <v>24</v>
@@ -10509,10 +10497,10 @@
         <v>5</v>
       </c>
       <c r="F301" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G301" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H301" s="17">
         <v>1005005</v>
@@ -10520,7 +10508,7 @@
     </row>
     <row r="302" spans="1:8">
       <c r="A302" s="11" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B302" s="11" t="s">
         <v>10</v>
@@ -10535,18 +10523,18 @@
         <v>48</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G302" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H302" s="20" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" s="11" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B303" s="11" t="s">
         <v>276</v>
@@ -10561,10 +10549,10 @@
         <v>27.1</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G303" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H303" s="17">
         <v>1006087</v>
@@ -10572,25 +10560,25 @@
     </row>
     <row r="304" spans="1:8">
       <c r="A304" s="11" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B304" s="11" t="s">
         <v>112</v>
       </c>
       <c r="C304" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="D304" s="11" t="s">
         <v>388</v>
-      </c>
-      <c r="D304" s="11" t="s">
-        <v>389</v>
       </c>
       <c r="E304" s="11">
         <v>240</v>
       </c>
       <c r="F304" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G304" s="19" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="H304" s="17">
         <v>2001060</v>
@@ -10598,25 +10586,25 @@
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="11" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B305" s="11" t="s">
         <v>112</v>
       </c>
       <c r="C305" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="D305" s="11" t="s">
         <v>388</v>
-      </c>
-      <c r="D305" s="11" t="s">
-        <v>389</v>
       </c>
       <c r="E305" s="11">
         <v>98</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G305" s="19" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="H305" s="17">
         <v>2001061</v>
@@ -10624,7 +10612,7 @@
     </row>
     <row r="306" spans="1:8">
       <c r="A306" s="11" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B306" s="11" t="s">
         <v>24</v>
@@ -10642,7 +10630,7 @@
         <v>271</v>
       </c>
       <c r="G306" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H306" s="17">
         <v>1006088</v>
@@ -10650,7 +10638,7 @@
     </row>
     <row r="307" spans="1:8">
       <c r="A307" s="11" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B307" s="11" t="s">
         <v>35</v>
@@ -10666,7 +10654,7 @@
         <v>271</v>
       </c>
       <c r="G307" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H307" s="17">
         <v>1006089</v>
@@ -10674,7 +10662,7 @@
     </row>
     <row r="308" spans="1:8">
       <c r="A308" s="11" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B308" s="11" t="s">
         <v>10</v>
@@ -10689,10 +10677,10 @@
         <v>22</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>127</v>
+        <v>613</v>
       </c>
       <c r="G308" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H308" s="17">
         <v>1006090</v>
@@ -10700,7 +10688,7 @@
     </row>
     <row r="309" spans="1:8">
       <c r="A309" s="11" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B309" s="11" t="s">
         <v>35</v>
@@ -10714,11 +10702,11 @@
       <c r="E309" s="11">
         <v>48</v>
       </c>
-      <c r="F309" s="11" t="s">
-        <v>355</v>
+      <c r="F309" s="4" t="s">
+        <v>354</v>
       </c>
       <c r="G309" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H309" s="17">
         <v>1006091</v>
@@ -10726,7 +10714,7 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310" s="11" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B310" s="11" t="s">
         <v>35</v>
@@ -10741,7 +10729,7 @@
         <v>110</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G310" s="9" t="s">
         <v>109</v>
@@ -10752,7 +10740,7 @@
     </row>
     <row r="311" spans="1:8">
       <c r="A311" s="11" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B311" s="11" t="s">
         <v>10</v>
@@ -10767,7 +10755,7 @@
         <v>68</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G311" s="9" t="s">
         <v>109</v>
@@ -10778,7 +10766,7 @@
     </row>
     <row r="312" spans="1:8">
       <c r="A312" s="11" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B312" s="11" t="s">
         <v>10</v>
@@ -10793,10 +10781,10 @@
         <v>32</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>127</v>
+        <v>613</v>
       </c>
       <c r="G312" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H312" s="17">
         <v>1006063</v>
@@ -10804,7 +10792,7 @@
     </row>
     <row r="313" spans="1:8">
       <c r="A313" s="11" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B313" s="11" t="s">
         <v>112</v>
@@ -10813,16 +10801,16 @@
         <v>25</v>
       </c>
       <c r="D313" s="11" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E313" s="11">
         <v>450</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G313" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H313" s="17">
         <v>1006092</v>
@@ -10830,22 +10818,22 @@
     </row>
     <row r="314" spans="1:8">
       <c r="A314" s="11" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B314" s="11" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C314" s="9" t="s">
         <v>19</v>
       </c>
       <c r="D314" s="11" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E314" s="11">
         <v>7.8</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G314" s="9" t="s">
         <v>109</v>
@@ -10856,7 +10844,7 @@
     </row>
     <row r="315" spans="1:8">
       <c r="A315" s="11" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B315" s="11" t="s">
         <v>10</v>
@@ -10871,10 +10859,10 @@
         <v>14.5</v>
       </c>
       <c r="F315" s="11" t="s">
-        <v>127</v>
+        <v>613</v>
       </c>
       <c r="G315" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H315" s="17">
         <v>1003005</v>
@@ -10882,25 +10870,25 @@
     </row>
     <row r="316" spans="1:8">
       <c r="A316" s="11" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B316" s="11" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C316" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="E316" s="11">
         <v>32.5</v>
       </c>
       <c r="F316" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G316" s="19" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="H316" s="17">
         <v>2001062</v>
@@ -10908,25 +10896,25 @@
     </row>
     <row r="317" spans="1:8">
       <c r="A317" s="11" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B317" s="11" t="s">
         <v>102</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E317" s="11">
         <v>9.5</v>
       </c>
       <c r="F317" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G317" s="19" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="H317" s="17">
         <v>2001063</v>
@@ -10934,22 +10922,22 @@
     </row>
     <row r="318" spans="1:8">
       <c r="A318" s="11" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B318" s="11" t="s">
         <v>276</v>
       </c>
       <c r="C318" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E318" s="11">
         <v>630</v>
       </c>
       <c r="F318" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G318" s="9" t="s">
         <v>15</v>
@@ -10960,7 +10948,7 @@
     </row>
     <row r="319" spans="1:8">
       <c r="A319" s="11" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B319" s="11" t="s">
         <v>35</v>
@@ -10974,8 +10962,8 @@
       <c r="E319" s="11">
         <v>23</v>
       </c>
-      <c r="F319" s="11" t="s">
-        <v>355</v>
+      <c r="F319" s="4" t="s">
+        <v>354</v>
       </c>
       <c r="G319" s="9" t="s">
         <v>15</v>
@@ -10986,7 +10974,7 @@
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="11" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B320" s="11" t="s">
         <v>10</v>
@@ -11001,10 +10989,10 @@
         <v>8</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G320" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H320" s="17">
         <v>1001200</v>
@@ -11012,7 +11000,7 @@
     </row>
     <row r="321" spans="1:8">
       <c r="A321" s="11" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B321" s="11" t="s">
         <v>10</v>
@@ -11027,10 +11015,10 @@
         <v>18</v>
       </c>
       <c r="F321" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G321" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H321" s="17">
         <v>1001201</v>
@@ -11038,7 +11026,7 @@
     </row>
     <row r="322" spans="1:8">
       <c r="A322" s="11" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B322" s="11" t="s">
         <v>10</v>
@@ -11053,10 +11041,10 @@
         <v>18</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G322" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H322" s="17">
         <v>1001202</v>
@@ -11064,7 +11052,7 @@
     </row>
     <row r="323" spans="1:8">
       <c r="A323" s="11" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B323" s="11" t="s">
         <v>10</v>
@@ -11079,10 +11067,10 @@
         <v>3</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G323" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H323" s="17">
         <v>1001203</v>
@@ -11090,7 +11078,7 @@
     </row>
     <row r="324" spans="1:8">
       <c r="A324" s="11" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B324" s="11" t="s">
         <v>10</v>
@@ -11105,10 +11093,10 @@
         <v>8</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G324" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H324" s="17">
         <v>1001204</v>
@@ -11116,7 +11104,7 @@
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="11" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B325" s="11" t="s">
         <v>10</v>
@@ -11131,10 +11119,10 @@
         <v>8</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G325" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H325" s="17">
         <v>1001205</v>
@@ -11142,7 +11130,7 @@
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="11" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B326" s="11" t="s">
         <v>10</v>
@@ -11157,10 +11145,10 @@
         <v>3</v>
       </c>
       <c r="F326" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G326" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H326" s="17">
         <v>1001206</v>
@@ -11168,7 +11156,7 @@
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="11" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B327" s="11" t="s">
         <v>10</v>
@@ -11183,10 +11171,10 @@
         <v>3</v>
       </c>
       <c r="F327" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G327" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H327" s="17">
         <v>1001207</v>
@@ -11194,7 +11182,7 @@
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="11" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B328" s="11" t="s">
         <v>10</v>
@@ -11209,10 +11197,10 @@
         <v>18</v>
       </c>
       <c r="F328" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G328" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H328" s="17">
         <v>1001208</v>
@@ -11220,7 +11208,7 @@
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="11" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B329" s="11" t="s">
         <v>10</v>
@@ -11235,10 +11223,10 @@
         <v>5</v>
       </c>
       <c r="F329" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G329" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H329" s="17">
         <v>1001209</v>
@@ -11246,7 +11234,7 @@
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="11" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B330" s="11" t="s">
         <v>10</v>
@@ -11261,10 +11249,10 @@
         <v>5</v>
       </c>
       <c r="F330" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G330" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H330" s="17">
         <v>1001210</v>
@@ -11272,7 +11260,7 @@
     </row>
     <row r="331" spans="1:8">
       <c r="A331" s="11" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B331" s="11" t="s">
         <v>10</v>
@@ -11287,10 +11275,10 @@
         <v>5</v>
       </c>
       <c r="F331" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G331" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H331" s="17">
         <v>1001211</v>
@@ -11298,7 +11286,7 @@
     </row>
     <row r="332" spans="1:8">
       <c r="A332" s="11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B332" s="11" t="s">
         <v>10</v>
@@ -11313,10 +11301,10 @@
         <v>8</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G332" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H332" s="17">
         <v>1001212</v>
@@ -11324,7 +11312,7 @@
     </row>
     <row r="333" spans="1:8">
       <c r="A333" s="11" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B333" s="11" t="s">
         <v>10</v>
@@ -11339,10 +11327,10 @@
         <v>2</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G333" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H333" s="17">
         <v>1001213</v>
@@ -11350,7 +11338,7 @@
     </row>
     <row r="334" spans="1:8">
       <c r="A334" s="11" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B334" s="11" t="s">
         <v>10</v>
@@ -11365,10 +11353,10 @@
         <v>8</v>
       </c>
       <c r="F334" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G334" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H334" s="17">
         <v>1001214</v>
@@ -11376,7 +11364,7 @@
     </row>
     <row r="335" spans="1:8">
       <c r="A335" s="11" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B335" s="11" t="s">
         <v>10</v>
@@ -11391,10 +11379,10 @@
         <v>6</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G335" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H335" s="17">
         <v>1001215</v>
@@ -11402,7 +11390,7 @@
     </row>
     <row r="336" spans="1:8">
       <c r="A336" s="11" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B336" s="11" t="s">
         <v>10</v>
@@ -11417,10 +11405,10 @@
         <v>6</v>
       </c>
       <c r="F336" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G336" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H336" s="17">
         <v>1001216</v>
@@ -11443,10 +11431,10 @@
         <v>6</v>
       </c>
       <c r="F337" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G337" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H337" s="17">
         <v>1001217</v>
@@ -11454,7 +11442,7 @@
     </row>
     <row r="338" spans="1:8">
       <c r="A338" s="11" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B338" s="11" t="s">
         <v>10</v>
@@ -11469,10 +11457,10 @@
         <v>4</v>
       </c>
       <c r="F338" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G338" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H338" s="17">
         <v>1001218</v>
@@ -11480,7 +11468,7 @@
     </row>
     <row r="339" spans="1:8">
       <c r="A339" s="11" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B339" s="11" t="s">
         <v>10</v>
@@ -11495,10 +11483,10 @@
         <v>3</v>
       </c>
       <c r="F339" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G339" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H339" s="17">
         <v>1001219</v>
@@ -11506,7 +11494,7 @@
     </row>
     <row r="340" spans="1:8">
       <c r="A340" s="11" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B340" s="11" t="s">
         <v>10</v>
@@ -11521,10 +11509,10 @@
         <v>3</v>
       </c>
       <c r="F340" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G340" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H340" s="17">
         <v>1001220</v>
@@ -11532,7 +11520,7 @@
     </row>
     <row r="341" spans="1:8">
       <c r="A341" s="11" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B341" s="11" t="s">
         <v>35</v>
@@ -11547,10 +11535,10 @@
         <v>18</v>
       </c>
       <c r="F341" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G341" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H341" s="17">
         <v>1001221</v>
@@ -11558,7 +11546,7 @@
     </row>
     <row r="342" spans="1:8">
       <c r="A342" s="11" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B342" s="11" t="s">
         <v>10</v>
@@ -11573,10 +11561,10 @@
         <v>5</v>
       </c>
       <c r="F342" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G342" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H342" s="17">
         <v>1001222</v>
@@ -11584,7 +11572,7 @@
     </row>
     <row r="343" spans="1:8">
       <c r="A343" s="11" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B343" s="11" t="s">
         <v>10</v>
@@ -11599,10 +11587,10 @@
         <v>5</v>
       </c>
       <c r="F343" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G343" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H343" s="17">
         <v>1001223</v>
@@ -11610,7 +11598,7 @@
     </row>
     <row r="344" spans="1:8">
       <c r="A344" s="11" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B344" s="11" t="s">
         <v>10</v>
@@ -11625,10 +11613,10 @@
         <v>18</v>
       </c>
       <c r="F344" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G344" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H344" s="17">
         <v>1001224</v>
@@ -11636,7 +11624,7 @@
     </row>
     <row r="345" spans="1:8">
       <c r="A345" s="11" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="B345" s="11" t="s">
         <v>112</v>
@@ -11650,8 +11638,8 @@
       <c r="E345" s="11">
         <v>125</v>
       </c>
-      <c r="F345" s="11" t="s">
-        <v>618</v>
+      <c r="F345" s="4" t="s">
+        <v>354</v>
       </c>
       <c r="G345" s="9" t="s">
         <v>15</v>
@@ -11662,7 +11650,7 @@
     </row>
     <row r="346" spans="1:8">
       <c r="A346" s="11" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="B346" s="11" t="s">
         <v>35</v>
@@ -11676,8 +11664,8 @@
       <c r="E346" s="11">
         <v>19.3</v>
       </c>
-      <c r="F346" s="11" t="s">
-        <v>618</v>
+      <c r="F346" s="4" t="s">
+        <v>354</v>
       </c>
       <c r="G346" s="9" t="s">
         <v>15</v>
@@ -11688,7 +11676,7 @@
     </row>
     <row r="347" spans="1:8">
       <c r="A347" s="11" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="B347" s="11" t="s">
         <v>35</v>
@@ -11697,7 +11685,7 @@
         <v>19</v>
       </c>
       <c r="D347" s="11" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E347" s="11">
         <v>12</v>
@@ -11706,7 +11694,7 @@
         <v>14</v>
       </c>
       <c r="G347" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H347" s="17">
         <v>1009040</v>
@@ -11714,7 +11702,7 @@
     </row>
     <row r="348" spans="1:8">
       <c r="A348" s="11" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="B348" s="11" t="s">
         <v>10</v>
@@ -11729,18 +11717,18 @@
         <v>10</v>
       </c>
       <c r="F348" s="11" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G348" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H348" s="17">
-        <v>1003027</v>
+        <v>1003029</v>
       </c>
     </row>
     <row r="349" spans="1:8">
       <c r="A349" s="11" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="B349" s="11" t="s">
         <v>10</v>
@@ -11755,7 +11743,7 @@
         <v>54</v>
       </c>
       <c r="F349" s="11" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G349" s="9" t="s">
         <v>59</v>
@@ -12101,7 +12089,6 @@
     <ignoredError sqref="C31" numberStoredAsText="1"/>
     <ignoredError sqref="D31" numberStoredAsText="1"/>
     <ignoredError sqref="E31" numberStoredAsText="1"/>
-    <ignoredError sqref="F31" numberStoredAsText="1"/>
     <ignoredError sqref="G31" numberStoredAsText="1"/>
     <ignoredError sqref="A32" numberStoredAsText="1"/>
     <ignoredError sqref="B32" numberStoredAsText="1"/>
@@ -12621,19 +12608,14 @@
     <ignoredError sqref="F98" numberStoredAsText="1"/>
     <ignoredError sqref="G98" numberStoredAsText="1"/>
     <ignoredError sqref="H98" numberStoredAsText="1"/>
-    <ignoredError sqref="A99" numberStoredAsText="1"/>
     <ignoredError sqref="B99" numberStoredAsText="1"/>
     <ignoredError sqref="C99" numberStoredAsText="1"/>
-    <ignoredError sqref="D99" numberStoredAsText="1"/>
-    <ignoredError sqref="E99" numberStoredAsText="1"/>
     <ignoredError sqref="F99" numberStoredAsText="1"/>
     <ignoredError sqref="G99" numberStoredAsText="1"/>
     <ignoredError sqref="H99" numberStoredAsText="1"/>
     <ignoredError sqref="A100" numberStoredAsText="1"/>
     <ignoredError sqref="B100" numberStoredAsText="1"/>
     <ignoredError sqref="C100" numberStoredAsText="1"/>
-    <ignoredError sqref="D100" numberStoredAsText="1"/>
-    <ignoredError sqref="E100" numberStoredAsText="1"/>
     <ignoredError sqref="F100" numberStoredAsText="1"/>
     <ignoredError sqref="G100" numberStoredAsText="1"/>
     <ignoredError sqref="H100" numberStoredAsText="1"/>
@@ -12662,16 +12644,12 @@
     <ignoredError sqref="A104" numberStoredAsText="1"/>
     <ignoredError sqref="B104" numberStoredAsText="1"/>
     <ignoredError sqref="C104" numberStoredAsText="1"/>
-    <ignoredError sqref="D104" numberStoredAsText="1"/>
-    <ignoredError sqref="E104" numberStoredAsText="1"/>
     <ignoredError sqref="F104" numberStoredAsText="1"/>
     <ignoredError sqref="G104" numberStoredAsText="1"/>
     <ignoredError sqref="H104" numberStoredAsText="1"/>
     <ignoredError sqref="A105" numberStoredAsText="1"/>
     <ignoredError sqref="B105" numberStoredAsText="1"/>
     <ignoredError sqref="C105" numberStoredAsText="1"/>
-    <ignoredError sqref="D105" numberStoredAsText="1"/>
-    <ignoredError sqref="E105" numberStoredAsText="1"/>
     <ignoredError sqref="F105" numberStoredAsText="1"/>
     <ignoredError sqref="G105" numberStoredAsText="1"/>
     <ignoredError sqref="A106" numberStoredAsText="1"/>
@@ -12765,7 +12743,6 @@
     <ignoredError sqref="B117" numberStoredAsText="1"/>
     <ignoredError sqref="C117" numberStoredAsText="1"/>
     <ignoredError sqref="D117" numberStoredAsText="1"/>
-    <ignoredError sqref="E117" numberStoredAsText="1"/>
     <ignoredError sqref="F117" numberStoredAsText="1"/>
     <ignoredError sqref="G117" numberStoredAsText="1"/>
     <ignoredError sqref="H117" numberStoredAsText="1"/>
@@ -12857,7 +12834,6 @@
     <ignoredError sqref="C130" numberStoredAsText="1"/>
     <ignoredError sqref="D130" numberStoredAsText="1"/>
     <ignoredError sqref="E130" numberStoredAsText="1"/>
-    <ignoredError sqref="F130" numberStoredAsText="1"/>
     <ignoredError sqref="G130" numberStoredAsText="1"/>
     <ignoredError sqref="H130" numberStoredAsText="1"/>
     <ignoredError sqref="A131" numberStoredAsText="1"/>
@@ -12865,7 +12841,6 @@
     <ignoredError sqref="C131" numberStoredAsText="1"/>
     <ignoredError sqref="D131" numberStoredAsText="1"/>
     <ignoredError sqref="E131" numberStoredAsText="1"/>
-    <ignoredError sqref="F131" numberStoredAsText="1"/>
     <ignoredError sqref="G131" numberStoredAsText="1"/>
     <ignoredError sqref="A132" numberStoredAsText="1"/>
     <ignoredError sqref="B132" numberStoredAsText="1"/>
@@ -13435,9 +13410,6 @@
     <ignoredError sqref="H208" numberStoredAsText="1"/>
     <ignoredError sqref="A209" numberStoredAsText="1"/>
     <ignoredError sqref="B209" numberStoredAsText="1"/>
-    <ignoredError sqref="D209" numberStoredAsText="1"/>
-    <ignoredError sqref="E209" numberStoredAsText="1"/>
-    <ignoredError sqref="F209" numberStoredAsText="1"/>
     <ignoredError sqref="G209" numberStoredAsText="1"/>
     <ignoredError sqref="H209" numberStoredAsText="1"/>
     <ignoredError sqref="A210" numberStoredAsText="1"/>
@@ -13810,9 +13782,6 @@
     <ignoredError sqref="H258" numberStoredAsText="1"/>
     <ignoredError sqref="B259" numberStoredAsText="1"/>
     <ignoredError sqref="C259" numberStoredAsText="1"/>
-    <ignoredError sqref="D259" numberStoredAsText="1"/>
-    <ignoredError sqref="E259" numberStoredAsText="1"/>
-    <ignoredError sqref="F259" numberStoredAsText="1"/>
     <ignoredError sqref="G259" numberStoredAsText="1"/>
     <ignoredError sqref="H259" numberStoredAsText="1"/>
     <ignoredError sqref="A260" numberStoredAsText="1"/>
@@ -13855,7 +13824,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="G1" s="22" t="s">
         <v>7</v>
@@ -13892,7 +13861,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="24" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>18</v>
